--- a/research/traditional_assets/database/data/austria/austria_computer_services.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_computer_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09406057172882033</v>
+        <v>0.09386902635667116</v>
       </c>
       <c r="C2">
-        <v>1683.696976562761</v>
+        <v>1671.354764543696</v>
       </c>
       <c r="D2">
-        <v>1447.196976562761</v>
+        <v>1452.963764543696</v>
       </c>
       <c r="E2">
-        <v>-571.9</v>
+        <v>-553.7909999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18.109</v>
       </c>
       <c r="G2">
         <v>236.5</v>
@@ -1457,28 +1457,28 @@
         <v>101.075</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.9108827</v>
       </c>
       <c r="N2">
-        <v>101.075</v>
+        <v>100.1641173</v>
       </c>
       <c r="O2">
-        <v>24.258</v>
+        <v>24.039388152</v>
       </c>
       <c r="P2">
-        <v>76.81700000000001</v>
+        <v>76.124729148</v>
       </c>
       <c r="Q2">
-        <v>152.617</v>
+        <v>151.924729148</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09406057172882033</v>
+        <v>0.09443105692593047</v>
       </c>
       <c r="T2">
-        <v>0.9922881498763957</v>
+        <v>0.9999057154714065</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>110.9637936915478</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09386902635667116</v>
+        <v>0.093677480984522</v>
       </c>
       <c r="C3">
-        <v>1671.354764543696</v>
+        <v>1659.05869536787</v>
       </c>
       <c r="D3">
-        <v>1452.963764543696</v>
+        <v>1458.77669536787</v>
       </c>
       <c r="E3">
-        <v>-553.7909999999999</v>
+        <v>-535.682</v>
       </c>
       <c r="F3">
-        <v>18.109</v>
+        <v>36.218</v>
       </c>
       <c r="G3">
         <v>236.5</v>
@@ -1539,28 +1539,28 @@
         <v>101.075</v>
       </c>
       <c r="M3">
-        <v>0.9108827</v>
+        <v>1.8217654</v>
       </c>
       <c r="N3">
-        <v>100.1641173</v>
+        <v>99.2532346</v>
       </c>
       <c r="O3">
-        <v>24.039388152</v>
+        <v>23.820776304</v>
       </c>
       <c r="P3">
-        <v>76.124729148</v>
+        <v>75.43245829599999</v>
       </c>
       <c r="Q3">
-        <v>151.924729148</v>
+        <v>151.232458296</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09443105692593047</v>
+        <v>0.09480910304543061</v>
       </c>
       <c r="T3">
-        <v>0.9999057154714065</v>
+        <v>1.007678741588764</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>110.9637936915478</v>
+        <v>55.48189684577388</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.093677480984522</v>
+        <v>0.09348593561237283</v>
       </c>
       <c r="C4">
-        <v>1659.05869536787</v>
+        <v>1646.809325076473</v>
       </c>
       <c r="D4">
-        <v>1458.77669536787</v>
+        <v>1464.636325076473</v>
       </c>
       <c r="E4">
-        <v>-535.682</v>
+        <v>-517.573</v>
       </c>
       <c r="F4">
-        <v>36.218</v>
+        <v>54.327</v>
       </c>
       <c r="G4">
         <v>236.5</v>
@@ -1621,28 +1621,28 @@
         <v>101.075</v>
       </c>
       <c r="M4">
-        <v>1.8217654</v>
+        <v>2.7326481</v>
       </c>
       <c r="N4">
-        <v>99.2532346</v>
+        <v>98.3423519</v>
       </c>
       <c r="O4">
-        <v>23.820776304</v>
+        <v>23.602164456</v>
       </c>
       <c r="P4">
-        <v>75.43245829599999</v>
+        <v>74.740187444</v>
       </c>
       <c r="Q4">
-        <v>151.232458296</v>
+        <v>150.540187444</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09480910304543061</v>
+        <v>0.09519494393028127</v>
       </c>
       <c r="T4">
-        <v>1.007678741588764</v>
+        <v>1.015612036285862</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>55.48189684577388</v>
+        <v>36.98793123051593</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09348593561237283</v>
+        <v>0.09329439024022365</v>
       </c>
       <c r="C5">
-        <v>1646.809325076473</v>
+        <v>1634.607218680771</v>
       </c>
       <c r="D5">
-        <v>1464.636325076473</v>
+        <v>1470.54321868077</v>
       </c>
       <c r="E5">
-        <v>-517.573</v>
+        <v>-499.4639999999999</v>
       </c>
       <c r="F5">
-        <v>54.327</v>
+        <v>72.43600000000001</v>
       </c>
       <c r="G5">
         <v>236.5</v>
@@ -1703,28 +1703,28 @@
         <v>101.075</v>
       </c>
       <c r="M5">
-        <v>2.7326481</v>
+        <v>3.6435308</v>
       </c>
       <c r="N5">
-        <v>98.3423519</v>
+        <v>97.43146920000001</v>
       </c>
       <c r="O5">
-        <v>23.602164456</v>
+        <v>23.383552608</v>
       </c>
       <c r="P5">
-        <v>74.740187444</v>
+        <v>74.04791659200001</v>
       </c>
       <c r="Q5">
-        <v>150.540187444</v>
+        <v>149.847916592</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09519494393028127</v>
+        <v>0.09558882316689965</v>
       </c>
       <c r="T5">
-        <v>1.015612036285862</v>
+        <v>1.023710607955815</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.98793123051593</v>
+        <v>27.74094842288694</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09329439024022365</v>
+        <v>0.09310284486807448</v>
       </c>
       <c r="C6">
-        <v>1634.607218680771</v>
+        <v>1622.452950343723</v>
       </c>
       <c r="D6">
-        <v>1470.54321868077</v>
+        <v>1476.497950343723</v>
       </c>
       <c r="E6">
-        <v>-499.4639999999999</v>
+        <v>-481.355</v>
       </c>
       <c r="F6">
-        <v>72.43600000000001</v>
+        <v>90.54500000000002</v>
       </c>
       <c r="G6">
         <v>236.5</v>
@@ -1785,28 +1785,28 @@
         <v>101.075</v>
       </c>
       <c r="M6">
-        <v>3.6435308</v>
+        <v>4.554413500000001</v>
       </c>
       <c r="N6">
-        <v>97.43146920000001</v>
+        <v>96.52058650000001</v>
       </c>
       <c r="O6">
-        <v>23.383552608</v>
+        <v>23.16494076</v>
       </c>
       <c r="P6">
-        <v>74.04791659200001</v>
+        <v>73.35564574</v>
       </c>
       <c r="Q6">
-        <v>149.847916592</v>
+        <v>149.15564574</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09558882316689965</v>
+        <v>0.09599099459797314</v>
       </c>
       <c r="T6">
-        <v>1.023710607955815</v>
+        <v>1.031979675871451</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.74094842288694</v>
+        <v>22.19275873830955</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09310284486807448</v>
+        <v>0.09291129949592532</v>
       </c>
       <c r="C7">
-        <v>1622.452950343723</v>
+        <v>1610.34710356603</v>
       </c>
       <c r="D7">
-        <v>1476.497950343723</v>
+        <v>1482.50110356603</v>
       </c>
       <c r="E7">
-        <v>-481.355</v>
+        <v>-463.246</v>
       </c>
       <c r="F7">
-        <v>90.54500000000002</v>
+        <v>108.654</v>
       </c>
       <c r="G7">
         <v>236.5</v>
@@ -1867,28 +1867,28 @@
         <v>101.075</v>
       </c>
       <c r="M7">
-        <v>4.554413500000001</v>
+        <v>5.4652962</v>
       </c>
       <c r="N7">
-        <v>96.52058650000001</v>
+        <v>95.60970380000001</v>
       </c>
       <c r="O7">
-        <v>23.16494076</v>
+        <v>22.946328912</v>
       </c>
       <c r="P7">
-        <v>73.35564574</v>
+        <v>72.66337488800001</v>
       </c>
       <c r="Q7">
-        <v>149.15564574</v>
+        <v>148.463374888</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09599099459797314</v>
+        <v>0.09640172286800566</v>
       </c>
       <c r="T7">
-        <v>1.031979675871451</v>
+        <v>1.040424681402315</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.19275873830955</v>
+        <v>18.49396561525796</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09291129949592532</v>
+        <v>0.09271975412377616</v>
       </c>
       <c r="C8">
-        <v>1610.34710356603</v>
+        <v>1598.290271376735</v>
       </c>
       <c r="D8">
-        <v>1482.50110356603</v>
+        <v>1488.553271376735</v>
       </c>
       <c r="E8">
-        <v>-463.246</v>
+        <v>-445.137</v>
       </c>
       <c r="F8">
-        <v>108.654</v>
+        <v>126.763</v>
       </c>
       <c r="G8">
         <v>236.5</v>
@@ -1949,28 +1949,28 @@
         <v>101.075</v>
       </c>
       <c r="M8">
-        <v>5.465296199999999</v>
+        <v>6.376178899999999</v>
       </c>
       <c r="N8">
-        <v>95.60970380000001</v>
+        <v>94.6988211</v>
       </c>
       <c r="O8">
-        <v>22.946328912</v>
+        <v>22.727717064</v>
       </c>
       <c r="P8">
-        <v>72.66337488800001</v>
+        <v>71.971104036</v>
       </c>
       <c r="Q8">
-        <v>148.463374888</v>
+        <v>147.771104036</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09640172286800566</v>
+        <v>0.09682128400406037</v>
       </c>
       <c r="T8">
-        <v>1.040424681402315</v>
+        <v>1.049051299955347</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.49396561525797</v>
+        <v>15.85197052736397</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09271975412377614</v>
+        <v>0.09252820875162698</v>
       </c>
       <c r="C9">
-        <v>1598.290271376736</v>
+        <v>1586.28305652851</v>
       </c>
       <c r="D9">
-        <v>1488.553271376736</v>
+        <v>1494.65505652851</v>
       </c>
       <c r="E9">
-        <v>-445.1369999999999</v>
+        <v>-427.028</v>
       </c>
       <c r="F9">
-        <v>126.763</v>
+        <v>144.872</v>
       </c>
       <c r="G9">
         <v>236.5</v>
@@ -2031,28 +2031,28 @@
         <v>101.075</v>
       </c>
       <c r="M9">
-        <v>6.376178900000001</v>
+        <v>7.2870616</v>
       </c>
       <c r="N9">
-        <v>94.6988211</v>
+        <v>93.7879384</v>
       </c>
       <c r="O9">
-        <v>22.727717064</v>
+        <v>22.509105216</v>
       </c>
       <c r="P9">
-        <v>71.971104036</v>
+        <v>71.27883318400001</v>
       </c>
       <c r="Q9">
-        <v>147.771104036</v>
+        <v>147.078833184</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09682128400406037</v>
+        <v>0.09724996603437715</v>
       </c>
       <c r="T9">
-        <v>1.049051299955347</v>
+        <v>1.057865453694314</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.85197052736397</v>
+        <v>13.87047421144347</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09252820875162698</v>
+        <v>0.09243926337947782</v>
       </c>
       <c r="C10">
-        <v>1586.28305652851</v>
+        <v>1571.024501424174</v>
       </c>
       <c r="D10">
-        <v>1494.65505652851</v>
+        <v>1497.505501424174</v>
       </c>
       <c r="E10">
-        <v>-427.028</v>
+        <v>-408.919</v>
       </c>
       <c r="F10">
-        <v>144.872</v>
+        <v>162.981</v>
       </c>
       <c r="G10">
         <v>236.5</v>
@@ -2113,45 +2113,45 @@
         <v>101.075</v>
       </c>
       <c r="M10">
-        <v>7.2870616</v>
+        <v>8.442415799999999</v>
       </c>
       <c r="N10">
-        <v>93.7879384</v>
+        <v>92.6325842</v>
       </c>
       <c r="O10">
-        <v>22.509105216</v>
+        <v>22.231820208</v>
       </c>
       <c r="P10">
-        <v>71.27883318400001</v>
+        <v>70.40076399199999</v>
       </c>
       <c r="Q10">
-        <v>147.078833184</v>
+        <v>146.200763992</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09724996603437715</v>
+        <v>0.09768806964777782</v>
       </c>
       <c r="T10">
-        <v>1.057865453694314</v>
+        <v>1.066873325097874</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.24</v>
       </c>
       <c r="W10">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.87047421144347</v>
+        <v>11.97228404694306</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09243926337947782</v>
+        <v>0.09225911800732865</v>
       </c>
       <c r="C11">
-        <v>1571.024501424174</v>
+        <v>1558.72208358544</v>
       </c>
       <c r="D11">
-        <v>1497.505501424174</v>
+        <v>1503.31208358544</v>
       </c>
       <c r="E11">
-        <v>-408.919</v>
+        <v>-390.8099999999999</v>
       </c>
       <c r="F11">
-        <v>162.981</v>
+        <v>181.09</v>
       </c>
       <c r="G11">
         <v>236.5</v>
@@ -2195,28 +2195,28 @@
         <v>101.075</v>
       </c>
       <c r="M11">
-        <v>8.442415799999999</v>
+        <v>9.380462</v>
       </c>
       <c r="N11">
-        <v>92.6325842</v>
+        <v>91.69453800000001</v>
       </c>
       <c r="O11">
-        <v>22.231820208</v>
+        <v>22.00668912</v>
       </c>
       <c r="P11">
-        <v>70.40076399199999</v>
+        <v>69.68784888</v>
       </c>
       <c r="Q11">
-        <v>146.200763992</v>
+        <v>145.48784888</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09768806964777782</v>
+        <v>0.09813590889703183</v>
       </c>
       <c r="T11">
-        <v>1.066873325097874</v>
+        <v>1.076081371421514</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.97228404694306</v>
+        <v>10.77505564224875</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09225911800732865</v>
+        <v>0.0922210926351795</v>
       </c>
       <c r="C12">
-        <v>1558.72208358544</v>
+        <v>1541.844506591441</v>
       </c>
       <c r="D12">
-        <v>1503.31208358544</v>
+        <v>1504.543506591441</v>
       </c>
       <c r="E12">
-        <v>-390.8099999999999</v>
+        <v>-372.701</v>
       </c>
       <c r="F12">
-        <v>181.09</v>
+        <v>199.199</v>
       </c>
       <c r="G12">
         <v>236.5</v>
@@ -2277,45 +2277,45 @@
         <v>101.075</v>
       </c>
       <c r="M12">
-        <v>9.380462000000001</v>
+        <v>10.6571465</v>
       </c>
       <c r="N12">
-        <v>91.69453799999999</v>
+        <v>90.41785350000001</v>
       </c>
       <c r="O12">
-        <v>22.00668912</v>
+        <v>21.70028484</v>
       </c>
       <c r="P12">
-        <v>69.68784887999999</v>
+        <v>68.71756866000001</v>
       </c>
       <c r="Q12">
-        <v>145.48784888</v>
+        <v>144.51756866</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09813590889703183</v>
+        <v>0.09859381194963987</v>
       </c>
       <c r="T12">
-        <v>1.076081371421514</v>
+        <v>1.085496340134448</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.24</v>
       </c>
       <c r="W12">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.77505564224875</v>
+        <v>9.484246087824729</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0922210926351795</v>
+        <v>0.0920538672630303</v>
       </c>
       <c r="C13">
-        <v>1541.844506591441</v>
+        <v>1529.175005225655</v>
       </c>
       <c r="D13">
-        <v>1504.543506591441</v>
+        <v>1509.983005225655</v>
       </c>
       <c r="E13">
-        <v>-372.701</v>
+        <v>-354.592</v>
       </c>
       <c r="F13">
-        <v>199.199</v>
+        <v>217.308</v>
       </c>
       <c r="G13">
         <v>236.5</v>
@@ -2359,28 +2359,28 @@
         <v>101.075</v>
       </c>
       <c r="M13">
-        <v>10.6571465</v>
+        <v>11.625978</v>
       </c>
       <c r="N13">
-        <v>90.41785350000001</v>
+        <v>89.449022</v>
       </c>
       <c r="O13">
-        <v>21.70028484</v>
+        <v>21.46776528</v>
       </c>
       <c r="P13">
-        <v>68.71756866000001</v>
+        <v>67.98125672</v>
       </c>
       <c r="Q13">
-        <v>144.51756866</v>
+        <v>143.78125672</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09859381194963987</v>
+        <v>0.09906212188980716</v>
       </c>
       <c r="T13">
-        <v>1.085496340134448</v>
+        <v>1.09512528540904</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.484246087824729</v>
+        <v>8.693892247172668</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0920538672630303</v>
+        <v>0.09188664189088114</v>
       </c>
       <c r="C14">
-        <v>1529.175005225655</v>
+        <v>1516.544978299581</v>
       </c>
       <c r="D14">
-        <v>1509.983005225655</v>
+        <v>1515.461978299581</v>
       </c>
       <c r="E14">
-        <v>-354.592</v>
+        <v>-336.4829999999999</v>
       </c>
       <c r="F14">
-        <v>217.308</v>
+        <v>235.417</v>
       </c>
       <c r="G14">
         <v>236.5</v>
@@ -2441,28 +2441,28 @@
         <v>101.075</v>
       </c>
       <c r="M14">
-        <v>11.625978</v>
+        <v>12.5948095</v>
       </c>
       <c r="N14">
-        <v>89.449022</v>
+        <v>88.48019050000001</v>
       </c>
       <c r="O14">
-        <v>21.46776528</v>
+        <v>21.23524572</v>
       </c>
       <c r="P14">
-        <v>67.98125672</v>
+        <v>67.24494478</v>
       </c>
       <c r="Q14">
-        <v>143.78125672</v>
+        <v>143.04494478</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09906212188980716</v>
+        <v>0.09954119757572545</v>
       </c>
       <c r="T14">
-        <v>1.09512528540904</v>
+        <v>1.104975585747416</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.693892247172668</v>
+        <v>8.025131305082462</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09188664189088114</v>
+        <v>0.09180453651873197</v>
       </c>
       <c r="C15">
-        <v>1516.544978299581</v>
+        <v>1501.140658731597</v>
       </c>
       <c r="D15">
-        <v>1515.461978299581</v>
+        <v>1518.166658731597</v>
       </c>
       <c r="E15">
-        <v>-336.4829999999999</v>
+        <v>-318.3739999999999</v>
       </c>
       <c r="F15">
-        <v>235.417</v>
+        <v>253.526</v>
       </c>
       <c r="G15">
         <v>236.5</v>
@@ -2523,45 +2523,45 @@
         <v>101.075</v>
       </c>
       <c r="M15">
-        <v>12.5948095</v>
+        <v>13.7664618</v>
       </c>
       <c r="N15">
-        <v>88.48019050000001</v>
+        <v>87.3085382</v>
       </c>
       <c r="O15">
-        <v>21.23524572</v>
+        <v>20.954049168</v>
       </c>
       <c r="P15">
-        <v>67.24494478</v>
+        <v>66.354489032</v>
       </c>
       <c r="Q15">
-        <v>143.04494478</v>
+        <v>142.154489032</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09954119757572545</v>
+        <v>0.1000314145566651</v>
       </c>
       <c r="T15">
-        <v>1.104975585747416</v>
+        <v>1.115054962837847</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.24</v>
       </c>
       <c r="W15">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.025131305082462</v>
+        <v>7.342118945915354</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09180453651873197</v>
+        <v>0.09164339114658282</v>
       </c>
       <c r="C16">
-        <v>1501.140658731597</v>
+        <v>1488.368208342936</v>
       </c>
       <c r="D16">
-        <v>1518.166658731597</v>
+        <v>1523.503208342936</v>
       </c>
       <c r="E16">
-        <v>-318.3739999999999</v>
+        <v>-300.2649999999999</v>
       </c>
       <c r="F16">
-        <v>253.526</v>
+        <v>271.635</v>
       </c>
       <c r="G16">
         <v>236.5</v>
@@ -2605,28 +2605,28 @@
         <v>101.075</v>
       </c>
       <c r="M16">
-        <v>13.7664618</v>
+        <v>14.7497805</v>
       </c>
       <c r="N16">
-        <v>87.3085382</v>
+        <v>86.3252195</v>
       </c>
       <c r="O16">
-        <v>20.954049168</v>
+        <v>20.71805268</v>
       </c>
       <c r="P16">
-        <v>66.354489032</v>
+        <v>65.60716682</v>
       </c>
       <c r="Q16">
-        <v>142.154489032</v>
+        <v>141.40716682</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1000314145566651</v>
+        <v>0.1005331660548033</v>
       </c>
       <c r="T16">
-        <v>1.115054962837847</v>
+        <v>1.125371501742171</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.342118945915354</v>
+        <v>6.852644349520997</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09164339114658279</v>
+        <v>0.09148224577443363</v>
       </c>
       <c r="C17">
-        <v>1488.368208342937</v>
+        <v>1475.633407603873</v>
       </c>
       <c r="D17">
-        <v>1523.503208342937</v>
+        <v>1528.877407603873</v>
       </c>
       <c r="E17">
-        <v>-300.265</v>
+        <v>-282.1559999999999</v>
       </c>
       <c r="F17">
-        <v>271.635</v>
+        <v>289.744</v>
       </c>
       <c r="G17">
         <v>236.5</v>
@@ -2687,28 +2687,28 @@
         <v>101.075</v>
       </c>
       <c r="M17">
-        <v>14.7497805</v>
+        <v>15.7330992</v>
       </c>
       <c r="N17">
-        <v>86.3252195</v>
+        <v>85.3419008</v>
       </c>
       <c r="O17">
-        <v>20.71805268</v>
+        <v>20.482056192</v>
       </c>
       <c r="P17">
-        <v>65.60716682</v>
+        <v>64.859844608</v>
       </c>
       <c r="Q17">
-        <v>141.40716682</v>
+        <v>140.659844608</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1005331660548033</v>
+        <v>0.1010468640171829</v>
       </c>
       <c r="T17">
-        <v>1.125371501742171</v>
+        <v>1.135933672525169</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.852644349520999</v>
+        <v>6.424354077675935</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09148224577443363</v>
+        <v>0.09145030040228445</v>
       </c>
       <c r="C18">
-        <v>1475.633407603873</v>
+        <v>1458.594292299613</v>
       </c>
       <c r="D18">
-        <v>1528.877407603873</v>
+        <v>1529.947292299614</v>
       </c>
       <c r="E18">
-        <v>-282.1559999999999</v>
+        <v>-264.0469999999999</v>
       </c>
       <c r="F18">
-        <v>289.744</v>
+        <v>307.8530000000001</v>
       </c>
       <c r="G18">
         <v>236.5</v>
@@ -2769,45 +2769,45 @@
         <v>101.075</v>
       </c>
       <c r="M18">
-        <v>15.7330992</v>
+        <v>17.0242709</v>
       </c>
       <c r="N18">
-        <v>85.3419008</v>
+        <v>84.0507291</v>
       </c>
       <c r="O18">
-        <v>20.482056192</v>
+        <v>20.172174984</v>
       </c>
       <c r="P18">
-        <v>64.859844608</v>
+        <v>63.878554116</v>
       </c>
       <c r="Q18">
-        <v>140.659844608</v>
+        <v>139.678554116</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1010468640171829</v>
+        <v>0.1015729402437162</v>
       </c>
       <c r="T18">
-        <v>1.135933672525169</v>
+        <v>1.146750353447517</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.24</v>
       </c>
       <c r="W18">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.424354077675935</v>
+        <v>5.937111820747635</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09145030040228445</v>
+        <v>0.0912967550301353</v>
       </c>
       <c r="C19">
-        <v>1458.594292299613</v>
+        <v>1445.648656724376</v>
       </c>
       <c r="D19">
-        <v>1529.947292299614</v>
+        <v>1535.110656724376</v>
       </c>
       <c r="E19">
-        <v>-264.0469999999999</v>
+        <v>-245.9379999999999</v>
       </c>
       <c r="F19">
-        <v>307.8530000000001</v>
+        <v>325.962</v>
       </c>
       <c r="G19">
         <v>236.5</v>
@@ -2851,28 +2851,28 @@
         <v>101.075</v>
       </c>
       <c r="M19">
-        <v>17.0242709</v>
+        <v>18.0256986</v>
       </c>
       <c r="N19">
-        <v>84.0507291</v>
+        <v>83.0493014</v>
       </c>
       <c r="O19">
-        <v>20.172174984</v>
+        <v>19.931832336</v>
       </c>
       <c r="P19">
-        <v>63.878554116</v>
+        <v>63.11746906400001</v>
       </c>
       <c r="Q19">
-        <v>139.678554116</v>
+        <v>138.917469064</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1015729402437162</v>
+        <v>0.102111847597726</v>
       </c>
       <c r="T19">
-        <v>1.146750353447517</v>
+        <v>1.157830855855775</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.937111820747635</v>
+        <v>5.607272275150545</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09129675503013529</v>
+        <v>0.09114320965798614</v>
       </c>
       <c r="C20">
-        <v>1445.648656724376</v>
+        <v>1432.7379904739</v>
       </c>
       <c r="D20">
-        <v>1535.110656724376</v>
+        <v>1540.308990473901</v>
       </c>
       <c r="E20">
-        <v>-245.938</v>
+        <v>-227.829</v>
       </c>
       <c r="F20">
-        <v>325.962</v>
+        <v>344.071</v>
       </c>
       <c r="G20">
         <v>236.5</v>
@@ -2933,28 +2933,28 @@
         <v>101.075</v>
       </c>
       <c r="M20">
-        <v>18.0256986</v>
+        <v>19.0271263</v>
       </c>
       <c r="N20">
-        <v>83.0493014</v>
+        <v>82.0478737</v>
       </c>
       <c r="O20">
-        <v>19.931832336</v>
+        <v>19.691489688</v>
       </c>
       <c r="P20">
-        <v>63.11746906400001</v>
+        <v>62.356384012</v>
       </c>
       <c r="Q20">
-        <v>138.917469064</v>
+        <v>138.156384012</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.102111847597726</v>
+        <v>0.1026640613061557</v>
       </c>
       <c r="T20">
-        <v>1.157830855855775</v>
+        <v>1.169184950916089</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.607272275150546</v>
+        <v>5.312152681721568</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09114320965798614</v>
+        <v>0.09098966428583696</v>
       </c>
       <c r="C21">
-        <v>1432.7379904739</v>
+        <v>1419.862650004343</v>
       </c>
       <c r="D21">
-        <v>1540.308990473901</v>
+        <v>1545.542650004343</v>
       </c>
       <c r="E21">
-        <v>-227.829</v>
+        <v>-209.7199999999999</v>
       </c>
       <c r="F21">
-        <v>344.071</v>
+        <v>362.1800000000001</v>
       </c>
       <c r="G21">
         <v>236.5</v>
@@ -3015,28 +3015,28 @@
         <v>101.075</v>
       </c>
       <c r="M21">
-        <v>19.0271263</v>
+        <v>20.028554</v>
       </c>
       <c r="N21">
-        <v>82.0478737</v>
+        <v>81.046446</v>
       </c>
       <c r="O21">
-        <v>19.691489688</v>
+        <v>19.45114704</v>
       </c>
       <c r="P21">
-        <v>62.356384012</v>
+        <v>61.59529896000001</v>
       </c>
       <c r="Q21">
-        <v>138.156384012</v>
+        <v>137.39529896</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1026640613061557</v>
+        <v>0.1032300803572962</v>
       </c>
       <c r="T21">
-        <v>1.169184950916089</v>
+        <v>1.180822898352911</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.312152681721568</v>
+        <v>5.04654504763549</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09098966428583696</v>
+        <v>0.09083611891368779</v>
       </c>
       <c r="C22">
-        <v>1419.862650004343</v>
+        <v>1407.022996633038</v>
       </c>
       <c r="D22">
-        <v>1545.542650004343</v>
+        <v>1550.811996633038</v>
       </c>
       <c r="E22">
-        <v>-209.7199999999999</v>
+        <v>-191.6109999999999</v>
       </c>
       <c r="F22">
-        <v>362.1800000000001</v>
+        <v>380.289</v>
       </c>
       <c r="G22">
         <v>236.5</v>
@@ -3097,28 +3097,28 @@
         <v>101.075</v>
       </c>
       <c r="M22">
-        <v>20.028554</v>
+        <v>21.0299817</v>
       </c>
       <c r="N22">
-        <v>81.046446</v>
+        <v>80.0450183</v>
       </c>
       <c r="O22">
-        <v>19.45114704</v>
+        <v>19.210804392</v>
       </c>
       <c r="P22">
-        <v>61.59529896000001</v>
+        <v>60.834213908</v>
       </c>
       <c r="Q22">
-        <v>137.39529896</v>
+        <v>136.634213908</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1032300803572962</v>
+        <v>0.1038104290046681</v>
       </c>
       <c r="T22">
-        <v>1.180822898352911</v>
+        <v>1.192755477370412</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.04654504763549</v>
+        <v>4.806233378700466</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09083611891368779</v>
+        <v>0.09068257354153864</v>
       </c>
       <c r="C23">
-        <v>1407.022996633038</v>
+        <v>1394.219396621655</v>
       </c>
       <c r="D23">
-        <v>1550.811996633038</v>
+        <v>1556.117396621655</v>
       </c>
       <c r="E23">
-        <v>-191.611</v>
+        <v>-173.502</v>
       </c>
       <c r="F23">
-        <v>380.289</v>
+        <v>398.398</v>
       </c>
       <c r="G23">
         <v>236.5</v>
@@ -3179,28 +3179,28 @@
         <v>101.075</v>
       </c>
       <c r="M23">
-        <v>21.0299817</v>
+        <v>22.0314094</v>
       </c>
       <c r="N23">
-        <v>80.04501830000001</v>
+        <v>79.0435906</v>
       </c>
       <c r="O23">
-        <v>19.210804392</v>
+        <v>18.970461744</v>
       </c>
       <c r="P23">
-        <v>60.83421390800001</v>
+        <v>60.073128856</v>
       </c>
       <c r="Q23">
-        <v>136.634213908</v>
+        <v>135.873128856</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1038104290046681</v>
+        <v>0.104405658386588</v>
       </c>
       <c r="T23">
-        <v>1.192755477370412</v>
+        <v>1.204994019952464</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.806233378700467</v>
+        <v>4.587768225123174</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09068257354153864</v>
+        <v>0.09096602816938947</v>
       </c>
       <c r="C24">
-        <v>1394.219396621655</v>
+        <v>1366.344457586738</v>
       </c>
       <c r="D24">
-        <v>1556.117396621655</v>
+        <v>1546.351457586738</v>
       </c>
       <c r="E24">
-        <v>-173.502</v>
+        <v>-155.3929999999999</v>
       </c>
       <c r="F24">
-        <v>398.398</v>
+        <v>416.5070000000001</v>
       </c>
       <c r="G24">
         <v>236.5</v>
@@ -3261,45 +3261,45 @@
         <v>101.075</v>
       </c>
       <c r="M24">
-        <v>22.0314094</v>
+        <v>24.07410460000001</v>
       </c>
       <c r="N24">
-        <v>79.0435906</v>
+        <v>77.00089539999999</v>
       </c>
       <c r="O24">
-        <v>18.970461744</v>
+        <v>18.480214896</v>
       </c>
       <c r="P24">
-        <v>60.073128856</v>
+        <v>58.520680504</v>
       </c>
       <c r="Q24">
-        <v>135.873128856</v>
+        <v>134.320680504</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.104405658386588</v>
+        <v>0.1050163482719344</v>
       </c>
       <c r="T24">
-        <v>1.204994019952464</v>
+        <v>1.217550446757427</v>
       </c>
       <c r="U24">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.24</v>
       </c>
       <c r="W24">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.587768225123174</v>
+        <v>4.19849467630875</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09096602816938947</v>
+        <v>0.09083148279724029</v>
       </c>
       <c r="C25">
-        <v>1366.344457586738</v>
+        <v>1352.855657042998</v>
       </c>
       <c r="D25">
-        <v>1546.351457586738</v>
+        <v>1550.971657042998</v>
       </c>
       <c r="E25">
-        <v>-155.3929999999999</v>
+        <v>-137.2839999999999</v>
       </c>
       <c r="F25">
-        <v>416.5070000000001</v>
+        <v>434.616</v>
       </c>
       <c r="G25">
         <v>236.5</v>
@@ -3343,28 +3343,28 @@
         <v>101.075</v>
       </c>
       <c r="M25">
-        <v>24.07410460000001</v>
+        <v>25.12080480000001</v>
       </c>
       <c r="N25">
-        <v>77.00089539999999</v>
+        <v>75.9541952</v>
       </c>
       <c r="O25">
-        <v>18.480214896</v>
+        <v>18.229006848</v>
       </c>
       <c r="P25">
-        <v>58.520680504</v>
+        <v>57.725188352</v>
       </c>
       <c r="Q25">
-        <v>134.320680504</v>
+        <v>133.525188352</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1050163482719344</v>
+        <v>0.1056431089437372</v>
       </c>
       <c r="T25">
-        <v>1.217550446757427</v>
+        <v>1.230437305846731</v>
       </c>
       <c r="U25">
         <v>0.0578</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.19849467630875</v>
+        <v>4.023557398129219</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09083148279724029</v>
+        <v>0.09136193742509112</v>
       </c>
       <c r="C26">
-        <v>1352.855657042998</v>
+        <v>1316.689477308345</v>
       </c>
       <c r="D26">
-        <v>1550.971657042998</v>
+        <v>1532.914477308345</v>
       </c>
       <c r="E26">
-        <v>-137.284</v>
+        <v>-119.175</v>
       </c>
       <c r="F26">
-        <v>434.616</v>
+        <v>452.725</v>
       </c>
       <c r="G26">
         <v>236.5</v>
@@ -3425,45 +3425,45 @@
         <v>101.075</v>
       </c>
       <c r="M26">
-        <v>25.1208048</v>
+        <v>27.7520425</v>
       </c>
       <c r="N26">
-        <v>75.9541952</v>
+        <v>73.3229575</v>
       </c>
       <c r="O26">
-        <v>18.229006848</v>
+        <v>17.5975098</v>
       </c>
       <c r="P26">
-        <v>57.725188352</v>
+        <v>55.7254477</v>
       </c>
       <c r="Q26">
-        <v>133.525188352</v>
+        <v>131.5254477</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1056431089437372</v>
+        <v>0.1062865832334548</v>
       </c>
       <c r="T26">
-        <v>1.230437305846731</v>
+        <v>1.243667814511749</v>
       </c>
       <c r="U26">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.023557398129219</v>
+        <v>3.64207427255129</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09136193742509112</v>
+        <v>0.09125399205294193</v>
       </c>
       <c r="C27">
-        <v>1316.689477308345</v>
+        <v>1302.220884151669</v>
       </c>
       <c r="D27">
-        <v>1532.914477308345</v>
+        <v>1536.554884151669</v>
       </c>
       <c r="E27">
-        <v>-119.175</v>
+        <v>-101.0659999999999</v>
       </c>
       <c r="F27">
-        <v>452.725</v>
+        <v>470.8340000000001</v>
       </c>
       <c r="G27">
         <v>236.5</v>
@@ -3507,28 +3507,28 @@
         <v>101.075</v>
       </c>
       <c r="M27">
-        <v>27.7520425</v>
+        <v>28.8621242</v>
       </c>
       <c r="N27">
-        <v>73.3229575</v>
+        <v>72.21287580000001</v>
       </c>
       <c r="O27">
-        <v>17.5975098</v>
+        <v>17.331090192</v>
       </c>
       <c r="P27">
-        <v>55.7254477</v>
+        <v>54.881785608</v>
       </c>
       <c r="Q27">
-        <v>131.5254477</v>
+        <v>130.681785608</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1062865832334548</v>
+        <v>0.1069474487201918</v>
       </c>
       <c r="T27">
-        <v>1.243667814511749</v>
+        <v>1.257255904492039</v>
       </c>
       <c r="U27">
         <v>0.0613</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.64207427255129</v>
+        <v>3.501994492837779</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09125399205294193</v>
+        <v>0.09172060668079277</v>
       </c>
       <c r="C28">
-        <v>1302.220884151669</v>
+        <v>1268.498436567565</v>
       </c>
       <c r="D28">
-        <v>1536.554884151669</v>
+        <v>1520.941436567565</v>
       </c>
       <c r="E28">
-        <v>-101.0659999999999</v>
+        <v>-82.95699999999994</v>
       </c>
       <c r="F28">
-        <v>470.8340000000001</v>
+        <v>488.943</v>
       </c>
       <c r="G28">
         <v>236.5</v>
@@ -3589,45 +3589,45 @@
         <v>101.075</v>
       </c>
       <c r="M28">
-        <v>28.8621242</v>
+        <v>31.34124630000001</v>
       </c>
       <c r="N28">
-        <v>72.21287580000001</v>
+        <v>69.73375369999999</v>
       </c>
       <c r="O28">
-        <v>17.331090192</v>
+        <v>16.736100888</v>
       </c>
       <c r="P28">
-        <v>54.881785608</v>
+        <v>52.997652812</v>
       </c>
       <c r="Q28">
-        <v>130.681785608</v>
+        <v>128.797652812</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1069474487201918</v>
+        <v>0.107626420110675</v>
       </c>
       <c r="T28">
-        <v>1.257255904492039</v>
+        <v>1.271216270910144</v>
       </c>
       <c r="U28">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V28">
         <v>0.24</v>
       </c>
       <c r="W28">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.501994492837779</v>
+        <v>3.22498343022179</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09172060668079277</v>
+        <v>0.09163394130864359</v>
       </c>
       <c r="C29">
-        <v>1268.498436567565</v>
+        <v>1253.265317450895</v>
       </c>
       <c r="D29">
-        <v>1520.941436567565</v>
+        <v>1523.817317450895</v>
       </c>
       <c r="E29">
-        <v>-82.95699999999994</v>
+        <v>-64.8479999999999</v>
       </c>
       <c r="F29">
-        <v>488.943</v>
+        <v>507.0520000000001</v>
       </c>
       <c r="G29">
         <v>236.5</v>
@@ -3671,28 +3671,28 @@
         <v>101.075</v>
       </c>
       <c r="M29">
-        <v>31.34124630000001</v>
+        <v>32.50203320000001</v>
       </c>
       <c r="N29">
-        <v>69.73375369999999</v>
+        <v>68.57296679999999</v>
       </c>
       <c r="O29">
-        <v>16.736100888</v>
+        <v>16.457512032</v>
       </c>
       <c r="P29">
-        <v>52.997652812</v>
+        <v>52.11545476799999</v>
       </c>
       <c r="Q29">
-        <v>128.797652812</v>
+        <v>127.915454768</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.107626420110675</v>
+        <v>0.1083242518175606</v>
       </c>
       <c r="T29">
-        <v>1.271216270910144</v>
+        <v>1.285564425284308</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.22498343022179</v>
+        <v>3.109805450571011</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09163394130864359</v>
+        <v>0.09154727593649443</v>
       </c>
       <c r="C30">
-        <v>1253.265317450895</v>
+        <v>1238.043094689556</v>
       </c>
       <c r="D30">
-        <v>1523.817317450895</v>
+        <v>1526.704094689556</v>
       </c>
       <c r="E30">
-        <v>-64.8479999999999</v>
+        <v>-46.73899999999992</v>
       </c>
       <c r="F30">
-        <v>507.0520000000001</v>
+        <v>525.1610000000001</v>
       </c>
       <c r="G30">
         <v>236.5</v>
@@ -3753,28 +3753,28 @@
         <v>101.075</v>
       </c>
       <c r="M30">
-        <v>32.50203320000001</v>
+        <v>33.6628201</v>
       </c>
       <c r="N30">
-        <v>68.57296679999999</v>
+        <v>67.4121799</v>
       </c>
       <c r="O30">
-        <v>16.457512032</v>
+        <v>16.178923176</v>
       </c>
       <c r="P30">
-        <v>52.11545476799999</v>
+        <v>51.233256724</v>
       </c>
       <c r="Q30">
-        <v>127.915454768</v>
+        <v>127.033256724</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1083242518175606</v>
+        <v>0.109041740755626</v>
       </c>
       <c r="T30">
-        <v>1.285564425284308</v>
+        <v>1.300316753021125</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.109805450571011</v>
+        <v>3.002570779861667</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09154727593649443</v>
+        <v>0.09323901056434525</v>
       </c>
       <c r="C31">
-        <v>1238.043094689556</v>
+        <v>1165.489911458443</v>
       </c>
       <c r="D31">
-        <v>1526.704094689556</v>
+        <v>1472.259911458443</v>
       </c>
       <c r="E31">
-        <v>-46.73900000000003</v>
+        <v>-28.63</v>
       </c>
       <c r="F31">
-        <v>525.1609999999999</v>
+        <v>543.27</v>
       </c>
       <c r="G31">
         <v>236.5</v>
@@ -3835,45 +3835,45 @@
         <v>101.075</v>
       </c>
       <c r="M31">
-        <v>33.6628201</v>
+        <v>39.061113</v>
       </c>
       <c r="N31">
-        <v>67.41217990000001</v>
+        <v>62.013887</v>
       </c>
       <c r="O31">
-        <v>16.178923176</v>
+        <v>14.88333288</v>
       </c>
       <c r="P31">
-        <v>51.23325672400001</v>
+        <v>47.13055412</v>
       </c>
       <c r="Q31">
-        <v>127.033256724</v>
+        <v>122.93055412</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.109041740755626</v>
+        <v>0.1097797293776361</v>
       </c>
       <c r="T31">
-        <v>1.300316753021125</v>
+        <v>1.315490575836136</v>
       </c>
       <c r="U31">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V31">
         <v>0.24</v>
       </c>
       <c r="W31">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.002570779861668</v>
+        <v>2.587611878852505</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09323901056434525</v>
+        <v>0.0932116251921961</v>
       </c>
       <c r="C32">
-        <v>1165.489911458443</v>
+        <v>1148.231301745891</v>
       </c>
       <c r="D32">
-        <v>1472.259911458443</v>
+        <v>1473.110301745891</v>
       </c>
       <c r="E32">
-        <v>-28.63</v>
+        <v>-10.52099999999996</v>
       </c>
       <c r="F32">
-        <v>543.27</v>
+        <v>561.379</v>
       </c>
       <c r="G32">
         <v>236.5</v>
@@ -3917,28 +3917,28 @@
         <v>101.075</v>
       </c>
       <c r="M32">
-        <v>39.061113</v>
+        <v>40.36315010000001</v>
       </c>
       <c r="N32">
-        <v>62.013887</v>
+        <v>60.7118499</v>
       </c>
       <c r="O32">
-        <v>14.88333288</v>
+        <v>14.570843976</v>
       </c>
       <c r="P32">
-        <v>47.13055412</v>
+        <v>46.141005924</v>
       </c>
       <c r="Q32">
-        <v>122.93055412</v>
+        <v>121.941005924</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1097797293776361</v>
+        <v>0.1105391089741972</v>
       </c>
       <c r="T32">
-        <v>1.315490575836136</v>
+        <v>1.331104219602307</v>
       </c>
       <c r="U32">
         <v>0.07190000000000001</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.587611878852505</v>
+        <v>2.504140527921779</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0932116251921961</v>
+        <v>0.09413271982004694</v>
       </c>
       <c r="C33">
-        <v>1148.231301745891</v>
+        <v>1102.048690531338</v>
       </c>
       <c r="D33">
-        <v>1473.110301745891</v>
+        <v>1445.036690531339</v>
       </c>
       <c r="E33">
-        <v>-10.52099999999996</v>
+        <v>7.588000000000079</v>
       </c>
       <c r="F33">
-        <v>561.379</v>
+        <v>579.4880000000001</v>
       </c>
       <c r="G33">
         <v>236.5</v>
@@ -3999,45 +3999,45 @@
         <v>101.075</v>
       </c>
       <c r="M33">
-        <v>40.36315010000001</v>
+        <v>43.92519040000001</v>
       </c>
       <c r="N33">
-        <v>60.7118499</v>
+        <v>57.1498096</v>
       </c>
       <c r="O33">
-        <v>14.570843976</v>
+        <v>13.715954304</v>
       </c>
       <c r="P33">
-        <v>46.141005924</v>
+        <v>43.433855296</v>
       </c>
       <c r="Q33">
-        <v>121.941005924</v>
+        <v>119.233855296</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1105391089741972</v>
+        <v>0.1113208232647749</v>
       </c>
       <c r="T33">
-        <v>1.331104219602307</v>
+        <v>1.34717708818513</v>
       </c>
       <c r="U33">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V33">
         <v>0.24</v>
       </c>
       <c r="W33">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.504140527921779</v>
+        <v>2.301071414365457</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09413271982004694</v>
+        <v>0.09413497444789776</v>
       </c>
       <c r="C34">
-        <v>1102.048690531338</v>
+        <v>1083.872285510334</v>
       </c>
       <c r="D34">
-        <v>1445.036690531339</v>
+        <v>1444.969285510334</v>
       </c>
       <c r="E34">
-        <v>7.588000000000079</v>
+        <v>25.69700000000012</v>
       </c>
       <c r="F34">
-        <v>579.4880000000001</v>
+        <v>597.5970000000001</v>
       </c>
       <c r="G34">
         <v>236.5</v>
@@ -4081,28 +4081,28 @@
         <v>101.075</v>
       </c>
       <c r="M34">
-        <v>43.92519040000001</v>
+        <v>45.29785260000001</v>
       </c>
       <c r="N34">
-        <v>57.1498096</v>
+        <v>55.77714739999999</v>
       </c>
       <c r="O34">
-        <v>13.715954304</v>
+        <v>13.386515376</v>
       </c>
       <c r="P34">
-        <v>43.433855296</v>
+        <v>42.39063202399999</v>
       </c>
       <c r="Q34">
-        <v>119.233855296</v>
+        <v>118.190632024</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1113208232647749</v>
+        <v>0.1121258723102952</v>
       </c>
       <c r="T34">
-        <v>1.34717708818513</v>
+        <v>1.363729743889829</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.301071414365457</v>
+        <v>2.231341977566503</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09413497444789776</v>
+        <v>0.09413722907574859</v>
       </c>
       <c r="C35">
-        <v>1083.872285510334</v>
+        <v>1065.695886777369</v>
       </c>
       <c r="D35">
-        <v>1444.969285510334</v>
+        <v>1444.90188677737</v>
       </c>
       <c r="E35">
-        <v>25.69700000000012</v>
+        <v>43.80600000000015</v>
       </c>
       <c r="F35">
-        <v>597.5970000000001</v>
+        <v>615.7060000000001</v>
       </c>
       <c r="G35">
         <v>236.5</v>
@@ -4163,28 +4163,28 @@
         <v>101.075</v>
       </c>
       <c r="M35">
-        <v>45.29785260000001</v>
+        <v>46.67051480000001</v>
       </c>
       <c r="N35">
-        <v>55.77714739999999</v>
+        <v>54.40448519999999</v>
       </c>
       <c r="O35">
-        <v>13.386515376</v>
+        <v>13.057076448</v>
       </c>
       <c r="P35">
-        <v>42.39063202399999</v>
+        <v>41.34740875199999</v>
       </c>
       <c r="Q35">
-        <v>118.190632024</v>
+        <v>117.147408752</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1121258723102952</v>
+        <v>0.1129553167814373</v>
       </c>
       <c r="T35">
-        <v>1.363729743889829</v>
+        <v>1.380783995221942</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.231341977566503</v>
+        <v>2.165714272343959</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09413722907574859</v>
+        <v>0.09413948370359942</v>
       </c>
       <c r="C36">
-        <v>1065.695886777369</v>
+        <v>1047.519494331566</v>
       </c>
       <c r="D36">
-        <v>1444.90188677737</v>
+        <v>1444.834494331566</v>
       </c>
       <c r="E36">
-        <v>43.80600000000015</v>
+        <v>61.91500000000008</v>
       </c>
       <c r="F36">
-        <v>615.7060000000001</v>
+        <v>633.8150000000001</v>
       </c>
       <c r="G36">
         <v>236.5</v>
@@ -4245,28 +4245,28 @@
         <v>101.075</v>
       </c>
       <c r="M36">
-        <v>46.67051480000001</v>
+        <v>48.04317700000001</v>
       </c>
       <c r="N36">
-        <v>54.40448519999999</v>
+        <v>53.031823</v>
       </c>
       <c r="O36">
-        <v>13.057076448</v>
+        <v>12.72763752</v>
       </c>
       <c r="P36">
-        <v>41.34740875199999</v>
+        <v>40.30418548</v>
       </c>
       <c r="Q36">
-        <v>117.147408752</v>
+        <v>116.10418548</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1129553167814373</v>
+        <v>0.1138102826209222</v>
       </c>
       <c r="T36">
-        <v>1.380783995221942</v>
+        <v>1.39836299274889</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.165714272343959</v>
+        <v>2.10383672170556</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09413948370359942</v>
+        <v>0.09414173833145026</v>
       </c>
       <c r="C37">
-        <v>1047.519494331566</v>
+        <v>1029.343108172044</v>
       </c>
       <c r="D37">
-        <v>1444.834494331566</v>
+        <v>1444.767108172044</v>
       </c>
       <c r="E37">
-        <v>61.91500000000008</v>
+        <v>80.02400000000011</v>
       </c>
       <c r="F37">
-        <v>633.8150000000001</v>
+        <v>651.9240000000001</v>
       </c>
       <c r="G37">
         <v>236.5</v>
@@ -4327,28 +4327,28 @@
         <v>101.075</v>
       </c>
       <c r="M37">
-        <v>48.04317700000001</v>
+        <v>49.41583920000001</v>
       </c>
       <c r="N37">
-        <v>53.031823</v>
+        <v>51.6591608</v>
       </c>
       <c r="O37">
-        <v>12.72763752</v>
+        <v>12.398198592</v>
       </c>
       <c r="P37">
-        <v>40.30418548</v>
+        <v>39.260962208</v>
       </c>
       <c r="Q37">
-        <v>116.10418548</v>
+        <v>115.060962208</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1138102826209222</v>
+        <v>0.114691966142891</v>
       </c>
       <c r="T37">
-        <v>1.39836299274889</v>
+        <v>1.416491333948555</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.10383672170556</v>
+        <v>2.045396812769295</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09414173833145024</v>
+        <v>0.09813703295930108</v>
       </c>
       <c r="C38">
-        <v>1029.343108172045</v>
+        <v>900.9437470378158</v>
       </c>
       <c r="D38">
-        <v>1444.767108172045</v>
+        <v>1334.476747037816</v>
       </c>
       <c r="E38">
-        <v>80.024</v>
+        <v>98.13300000000004</v>
       </c>
       <c r="F38">
-        <v>651.924</v>
+        <v>670.033</v>
       </c>
       <c r="G38">
         <v>236.5</v>
@@ -4409,45 +4409,45 @@
         <v>101.075</v>
       </c>
       <c r="M38">
-        <v>49.4158392</v>
+        <v>60.30297</v>
       </c>
       <c r="N38">
-        <v>51.6591608</v>
+        <v>40.77203</v>
       </c>
       <c r="O38">
-        <v>12.398198592</v>
+        <v>9.785287199999999</v>
       </c>
       <c r="P38">
-        <v>39.260962208</v>
+        <v>30.9867428</v>
       </c>
       <c r="Q38">
-        <v>115.060962208</v>
+        <v>106.7867428</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.114691966142891</v>
+        <v>0.1156016396179382</v>
       </c>
       <c r="T38">
-        <v>1.416491333948555</v>
+        <v>1.435195178043447</v>
       </c>
       <c r="U38">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V38">
         <v>0.24</v>
       </c>
       <c r="W38">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.045396812769295</v>
+        <v>1.676119766572028</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09813703295930108</v>
+        <v>0.09824720758715191</v>
       </c>
       <c r="C39">
-        <v>900.9437470378158</v>
+        <v>880.0314428059144</v>
       </c>
       <c r="D39">
-        <v>1334.476747037816</v>
+        <v>1331.673442805914</v>
       </c>
       <c r="E39">
-        <v>98.13300000000004</v>
+        <v>116.2420000000001</v>
       </c>
       <c r="F39">
-        <v>670.033</v>
+        <v>688.1420000000001</v>
       </c>
       <c r="G39">
         <v>236.5</v>
@@ -4491,28 +4491,28 @@
         <v>101.075</v>
       </c>
       <c r="M39">
-        <v>60.30297</v>
+        <v>61.93278</v>
       </c>
       <c r="N39">
-        <v>40.77203</v>
+        <v>39.14222</v>
       </c>
       <c r="O39">
-        <v>9.785287199999999</v>
+        <v>9.3941328</v>
       </c>
       <c r="P39">
-        <v>30.9867428</v>
+        <v>29.7480872</v>
       </c>
       <c r="Q39">
-        <v>106.7867428</v>
+        <v>105.5480872</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1156016396179382</v>
+        <v>0.1165406573986321</v>
       </c>
       <c r="T39">
-        <v>1.435195178043447</v>
+        <v>1.454502371947852</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.676119766572028</v>
+        <v>1.632011351662238</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09824720758715191</v>
+        <v>0.09835738221500276</v>
       </c>
       <c r="C40">
-        <v>880.0314428059144</v>
+        <v>859.1308915566568</v>
       </c>
       <c r="D40">
-        <v>1331.673442805914</v>
+        <v>1328.881891556657</v>
       </c>
       <c r="E40">
-        <v>116.2420000000001</v>
+        <v>134.3510000000001</v>
       </c>
       <c r="F40">
-        <v>688.1420000000001</v>
+        <v>706.2510000000001</v>
       </c>
       <c r="G40">
         <v>236.5</v>
@@ -4573,28 +4573,28 @@
         <v>101.075</v>
       </c>
       <c r="M40">
-        <v>61.93278</v>
+        <v>63.56259000000001</v>
       </c>
       <c r="N40">
-        <v>39.14222</v>
+        <v>37.51241</v>
       </c>
       <c r="O40">
-        <v>9.3941328</v>
+        <v>9.002978399999998</v>
       </c>
       <c r="P40">
-        <v>29.7480872</v>
+        <v>28.5094316</v>
       </c>
       <c r="Q40">
-        <v>105.5480872</v>
+        <v>104.3094316</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1165406573986321</v>
+        <v>0.1175104626475455</v>
       </c>
       <c r="T40">
-        <v>1.454502371947852</v>
+        <v>1.474442588603222</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.632011351662238</v>
+        <v>1.590164906747821</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09835738221500276</v>
+        <v>0.09846755684285358</v>
       </c>
       <c r="C41">
-        <v>859.1308915566568</v>
+        <v>838.2420195322757</v>
       </c>
       <c r="D41">
-        <v>1328.881891556657</v>
+        <v>1326.102019532276</v>
       </c>
       <c r="E41">
-        <v>134.3510000000001</v>
+        <v>152.4600000000002</v>
       </c>
       <c r="F41">
-        <v>706.2510000000001</v>
+        <v>724.3600000000001</v>
       </c>
       <c r="G41">
         <v>236.5</v>
@@ -4655,28 +4655,28 @@
         <v>101.075</v>
       </c>
       <c r="M41">
-        <v>63.56259000000001</v>
+        <v>65.19240000000001</v>
       </c>
       <c r="N41">
-        <v>37.51241</v>
+        <v>35.8826</v>
       </c>
       <c r="O41">
-        <v>9.002978399999998</v>
+        <v>8.611823999999999</v>
       </c>
       <c r="P41">
-        <v>28.5094316</v>
+        <v>27.270776</v>
       </c>
       <c r="Q41">
-        <v>104.3094316</v>
+        <v>103.070776</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1175104626475455</v>
+        <v>0.1185125947380893</v>
       </c>
       <c r="T41">
-        <v>1.474442588603222</v>
+        <v>1.495047479147103</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.590164906747821</v>
+        <v>1.550410784079126</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09846755684285358</v>
+        <v>0.09857773147070441</v>
       </c>
       <c r="C42">
-        <v>838.2420195322757</v>
+        <v>817.3647535908854</v>
       </c>
       <c r="D42">
-        <v>1326.102019532276</v>
+        <v>1323.333753590885</v>
       </c>
       <c r="E42">
-        <v>152.4600000000002</v>
+        <v>170.5690000000001</v>
       </c>
       <c r="F42">
-        <v>724.3600000000001</v>
+        <v>742.4690000000001</v>
       </c>
       <c r="G42">
         <v>236.5</v>
@@ -4737,28 +4737,28 @@
         <v>101.075</v>
       </c>
       <c r="M42">
-        <v>65.19240000000001</v>
+        <v>66.82221</v>
       </c>
       <c r="N42">
-        <v>35.8826</v>
+        <v>34.25279</v>
       </c>
       <c r="O42">
-        <v>8.611823999999999</v>
+        <v>8.220669600000001</v>
       </c>
       <c r="P42">
-        <v>27.270776</v>
+        <v>26.0321204</v>
       </c>
       <c r="Q42">
-        <v>103.070776</v>
+        <v>101.8321204</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1185125947380893</v>
+        <v>0.1195486974079736</v>
       </c>
       <c r="T42">
-        <v>1.495047479147103</v>
+        <v>1.516350840556878</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.550410784079126</v>
+        <v>1.512595886906464</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09857773147070441</v>
+        <v>0.1186812292179995</v>
       </c>
       <c r="C43">
-        <v>817.3647535908854</v>
+        <v>434.2284698899188</v>
       </c>
       <c r="D43">
-        <v>1323.333753590885</v>
+        <v>958.3064698899187</v>
       </c>
       <c r="E43">
-        <v>170.5690000000001</v>
+        <v>188.6780000000001</v>
       </c>
       <c r="F43">
-        <v>742.4690000000001</v>
+        <v>760.5780000000001</v>
       </c>
       <c r="G43">
         <v>236.5</v>
@@ -4819,45 +4819,45 @@
         <v>101.075</v>
       </c>
       <c r="M43">
-        <v>66.82221</v>
+        <v>111.6528504</v>
       </c>
       <c r="N43">
-        <v>34.25279</v>
+        <v>-10.57785040000002</v>
       </c>
       <c r="O43">
-        <v>8.220669600000001</v>
+        <v>-2.538684096000004</v>
       </c>
       <c r="P43">
-        <v>26.0321204</v>
+        <v>-8.039166304000013</v>
       </c>
       <c r="Q43">
-        <v>101.8321204</v>
+        <v>67.76083369599999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1195486974079736</v>
+        <v>0.1214151351593847</v>
       </c>
       <c r="T43">
-        <v>1.516350840556878</v>
+        <v>1.554726765185661</v>
       </c>
       <c r="U43">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.24</v>
+        <v>0.2172627023232718</v>
       </c>
       <c r="W43">
-        <v>0.0684</v>
+        <v>0.1149058352989437</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.512595886906464</v>
+        <v>0.9052612596802991</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1186812292179995</v>
+        <v>0.1196912292179995</v>
       </c>
       <c r="C44">
-        <v>434.2284698899189</v>
+        <v>403.0206279186574</v>
       </c>
       <c r="D44">
-        <v>958.3064698899187</v>
+        <v>945.2076279186574</v>
       </c>
       <c r="E44">
-        <v>188.678</v>
+        <v>206.787</v>
       </c>
       <c r="F44">
-        <v>760.578</v>
+        <v>778.687</v>
       </c>
       <c r="G44">
         <v>236.5</v>
@@ -4901,37 +4901,37 @@
         <v>101.075</v>
       </c>
       <c r="M44">
-        <v>111.6528504</v>
+        <v>114.3112516</v>
       </c>
       <c r="N44">
-        <v>-10.5778504</v>
+        <v>-13.2362516</v>
       </c>
       <c r="O44">
-        <v>-2.538684096</v>
+        <v>-3.176700384000001</v>
       </c>
       <c r="P44">
-        <v>-8.039166304000002</v>
+        <v>-10.059551216</v>
       </c>
       <c r="Q44">
-        <v>67.76083369599999</v>
+        <v>65.74044878399999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1214151351593847</v>
+        <v>0.1227417164779703</v>
       </c>
       <c r="T44">
-        <v>1.554726765185661</v>
+        <v>1.582002673346813</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.2172627023232718</v>
+        <v>0.2122100813390097</v>
       </c>
       <c r="W44">
-        <v>0.1149058352989437</v>
+        <v>0.1156475600594334</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.9052612596802991</v>
+        <v>0.8842086722458736</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1196912292179995</v>
+        <v>0.1207012292179994</v>
       </c>
       <c r="C45">
-        <v>403.0206279186574</v>
+        <v>372.1660466489654</v>
       </c>
       <c r="D45">
-        <v>945.2076279186574</v>
+        <v>932.4620466489655</v>
       </c>
       <c r="E45">
-        <v>206.787</v>
+        <v>224.8960000000001</v>
       </c>
       <c r="F45">
-        <v>778.687</v>
+        <v>796.796</v>
       </c>
       <c r="G45">
         <v>236.5</v>
@@ -4983,37 +4983,37 @@
         <v>101.075</v>
       </c>
       <c r="M45">
-        <v>114.3112516</v>
+        <v>116.9696528</v>
       </c>
       <c r="N45">
-        <v>-13.2362516</v>
+        <v>-15.89465280000002</v>
       </c>
       <c r="O45">
-        <v>-3.176700384000001</v>
+        <v>-3.814716672000004</v>
       </c>
       <c r="P45">
-        <v>-10.059551216</v>
+        <v>-12.07993612800001</v>
       </c>
       <c r="Q45">
-        <v>65.74044878399999</v>
+        <v>63.72006387199998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1227417164779703</v>
+        <v>0.1241156757007912</v>
       </c>
       <c r="T45">
-        <v>1.582002673346813</v>
+        <v>1.610252721085149</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.2122100813390097</v>
+        <v>0.2073871249449412</v>
       </c>
       <c r="W45">
-        <v>0.1156475600594334</v>
+        <v>0.1163555700580826</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8842086722458736</v>
+        <v>0.8641130206039218</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1207012292179994</v>
+        <v>0.1217112292179995</v>
       </c>
       <c r="C46">
-        <v>372.1660466489654</v>
+        <v>341.6506256646486</v>
       </c>
       <c r="D46">
-        <v>932.4620466489655</v>
+        <v>920.0556256646487</v>
       </c>
       <c r="E46">
-        <v>224.8960000000001</v>
+        <v>243.0050000000001</v>
       </c>
       <c r="F46">
-        <v>796.796</v>
+        <v>814.9050000000001</v>
       </c>
       <c r="G46">
         <v>236.5</v>
@@ -5065,37 +5065,37 @@
         <v>101.075</v>
       </c>
       <c r="M46">
-        <v>116.9696528</v>
+        <v>119.628054</v>
       </c>
       <c r="N46">
-        <v>-15.89465280000002</v>
+        <v>-18.55305400000002</v>
       </c>
       <c r="O46">
-        <v>-3.814716672000004</v>
+        <v>-4.452732960000004</v>
       </c>
       <c r="P46">
-        <v>-12.07993612800001</v>
+        <v>-14.10032104000001</v>
       </c>
       <c r="Q46">
-        <v>63.72006387199998</v>
+        <v>61.69967895999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1241156757007912</v>
+        <v>0.1255395970771693</v>
       </c>
       <c r="T46">
-        <v>1.610252721085149</v>
+        <v>1.639530043286697</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.2073871249449412</v>
+        <v>0.202778522168387</v>
       </c>
       <c r="W46">
-        <v>0.1163555700580826</v>
+        <v>0.1170321129456808</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8641130206039218</v>
+        <v>0.8449105090349458</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1217112292179995</v>
+        <v>0.1227212292179995</v>
       </c>
       <c r="C47">
-        <v>341.6506256646486</v>
+        <v>311.4610051211607</v>
       </c>
       <c r="D47">
-        <v>920.0556256646487</v>
+        <v>907.9750051211608</v>
       </c>
       <c r="E47">
-        <v>243.0050000000001</v>
+        <v>261.1140000000001</v>
       </c>
       <c r="F47">
-        <v>814.9050000000001</v>
+        <v>833.0140000000001</v>
       </c>
       <c r="G47">
         <v>236.5</v>
@@ -5147,37 +5147,37 @@
         <v>101.075</v>
       </c>
       <c r="M47">
-        <v>119.628054</v>
+        <v>122.2864552</v>
       </c>
       <c r="N47">
-        <v>-18.55305400000002</v>
+        <v>-21.21145520000003</v>
       </c>
       <c r="O47">
-        <v>-4.452732960000004</v>
+        <v>-5.090749248000008</v>
       </c>
       <c r="P47">
-        <v>-14.10032104000001</v>
+        <v>-16.12070595200002</v>
       </c>
       <c r="Q47">
-        <v>61.69967895999999</v>
+        <v>59.67929404799997</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1255395970771693</v>
+        <v>0.127016256282302</v>
       </c>
       <c r="T47">
-        <v>1.639530043286697</v>
+        <v>1.669891710754969</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.202778522168387</v>
+        <v>0.1983702934255959</v>
       </c>
       <c r="W47">
-        <v>0.1170321129456808</v>
+        <v>0.1176792409251225</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8449105090349458</v>
+        <v>0.8265428892733164</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1227212292179995</v>
+        <v>0.1237312292179995</v>
       </c>
       <c r="C48">
-        <v>311.4610051211607</v>
+        <v>281.5845177560241</v>
       </c>
       <c r="D48">
-        <v>907.9750051211608</v>
+        <v>896.2075177560241</v>
       </c>
       <c r="E48">
-        <v>261.1140000000001</v>
+        <v>279.2230000000001</v>
       </c>
       <c r="F48">
-        <v>833.0140000000001</v>
+        <v>851.123</v>
       </c>
       <c r="G48">
         <v>236.5</v>
@@ -5229,37 +5229,37 @@
         <v>101.075</v>
       </c>
       <c r="M48">
-        <v>122.2864552</v>
+        <v>124.9448564</v>
       </c>
       <c r="N48">
-        <v>-21.21145520000003</v>
+        <v>-23.86985640000002</v>
       </c>
       <c r="O48">
-        <v>-5.090749248000008</v>
+        <v>-5.728765536000004</v>
       </c>
       <c r="P48">
-        <v>-16.12070595200002</v>
+        <v>-18.14109086400001</v>
       </c>
       <c r="Q48">
-        <v>59.67929404799997</v>
+        <v>57.65890913599998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.127016256282302</v>
+        <v>0.1285486384763077</v>
       </c>
       <c r="T48">
-        <v>1.669891710754969</v>
+        <v>1.701399101523931</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.1983702934255959</v>
+        <v>0.1941496488846258</v>
       </c>
       <c r="W48">
-        <v>0.1176792409251225</v>
+        <v>0.1182988315437369</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8265428892733164</v>
+        <v>0.8089568703526077</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1237312292179995</v>
+        <v>0.1518455162706109</v>
       </c>
       <c r="C49">
-        <v>281.5845177560241</v>
+        <v>25.8772080961935</v>
       </c>
       <c r="D49">
-        <v>896.2075177560241</v>
+        <v>658.6092080961936</v>
       </c>
       <c r="E49">
-        <v>279.2230000000001</v>
+        <v>297.3320000000001</v>
       </c>
       <c r="F49">
-        <v>851.123</v>
+        <v>869.2320000000001</v>
       </c>
       <c r="G49">
         <v>236.5</v>
@@ -5311,45 +5311,45 @@
         <v>101.075</v>
       </c>
       <c r="M49">
-        <v>124.9448564</v>
+        <v>174.5417856</v>
       </c>
       <c r="N49">
-        <v>-23.86985640000002</v>
+        <v>-73.46678560000002</v>
       </c>
       <c r="O49">
-        <v>-5.728765536000004</v>
+        <v>-17.632028544</v>
       </c>
       <c r="P49">
-        <v>-18.14109086400001</v>
+        <v>-55.83475705600002</v>
       </c>
       <c r="Q49">
-        <v>57.65890913599998</v>
+        <v>19.96524294399998</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1285486384763077</v>
+        <v>0.1324174335481818</v>
       </c>
       <c r="T49">
-        <v>1.701399101523931</v>
+        <v>1.780945600179027</v>
       </c>
       <c r="U49">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1941496488846258</v>
+        <v>0.1389810463815949</v>
       </c>
       <c r="W49">
-        <v>0.1182988315437369</v>
+        <v>0.1728926058865757</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.8089568703526077</v>
+        <v>0.5790876932566456</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1518455162706109</v>
+        <v>0.1533955162706109</v>
       </c>
       <c r="C50">
-        <v>25.87720809619361</v>
+        <v>-1.719587566049313</v>
       </c>
       <c r="D50">
-        <v>658.6092080961936</v>
+        <v>649.1214124339507</v>
       </c>
       <c r="E50">
-        <v>297.332</v>
+        <v>315.441</v>
       </c>
       <c r="F50">
-        <v>869.232</v>
+        <v>887.341</v>
       </c>
       <c r="G50">
         <v>236.5</v>
@@ -5393,37 +5393,37 @@
         <v>101.075</v>
       </c>
       <c r="M50">
-        <v>174.5417856</v>
+        <v>178.1780728</v>
       </c>
       <c r="N50">
-        <v>-73.46678559999999</v>
+        <v>-77.10307279999999</v>
       </c>
       <c r="O50">
-        <v>-17.632028544</v>
+        <v>-18.504737472</v>
       </c>
       <c r="P50">
-        <v>-55.834757056</v>
+        <v>-58.59833532799999</v>
       </c>
       <c r="Q50">
-        <v>19.965242944</v>
+        <v>17.20166467200001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1324174335481818</v>
+        <v>0.1341158145981461</v>
       </c>
       <c r="T50">
-        <v>1.780945600179027</v>
+        <v>1.815866102143322</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1389810463815949</v>
+        <v>0.1361446984962563</v>
       </c>
       <c r="W50">
-        <v>0.1728926058865757</v>
+        <v>0.1734621445419517</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5790876932566456</v>
+        <v>0.5672695770677345</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1533955162706109</v>
+        <v>0.1549455162706109</v>
       </c>
       <c r="C51">
-        <v>-1.719587566049313</v>
+        <v>-29.04690659234848</v>
       </c>
       <c r="D51">
-        <v>649.1214124339507</v>
+        <v>639.9030934076516</v>
       </c>
       <c r="E51">
-        <v>315.441</v>
+        <v>333.5500000000001</v>
       </c>
       <c r="F51">
-        <v>887.341</v>
+        <v>905.45</v>
       </c>
       <c r="G51">
         <v>236.5</v>
@@ -5475,37 +5475,37 @@
         <v>101.075</v>
       </c>
       <c r="M51">
-        <v>178.1780728</v>
+        <v>181.81436</v>
       </c>
       <c r="N51">
-        <v>-77.10307279999999</v>
+        <v>-80.73936000000002</v>
       </c>
       <c r="O51">
-        <v>-18.504737472</v>
+        <v>-19.3774464</v>
       </c>
       <c r="P51">
-        <v>-58.59833532799999</v>
+        <v>-61.36191360000002</v>
       </c>
       <c r="Q51">
-        <v>17.20166467200001</v>
+        <v>14.43808639999998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1341158145981461</v>
+        <v>0.135882130890109</v>
       </c>
       <c r="T51">
-        <v>1.815866102143322</v>
+        <v>1.852183424186188</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1361446984962563</v>
+        <v>0.1334218045263311</v>
       </c>
       <c r="W51">
-        <v>0.1734621445419517</v>
+        <v>0.1740089016511127</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5672695770677345</v>
+        <v>0.5559241855263797</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1549455162706109</v>
+        <v>0.1564955162706109</v>
       </c>
       <c r="C52">
-        <v>-29.04690659234848</v>
+        <v>-56.11606892048792</v>
       </c>
       <c r="D52">
-        <v>639.9030934076516</v>
+        <v>630.9429310795122</v>
       </c>
       <c r="E52">
-        <v>333.5500000000001</v>
+        <v>351.6590000000001</v>
       </c>
       <c r="F52">
-        <v>905.45</v>
+        <v>923.5590000000001</v>
       </c>
       <c r="G52">
         <v>236.5</v>
@@ -5557,37 +5557,37 @@
         <v>101.075</v>
       </c>
       <c r="M52">
-        <v>181.81436</v>
+        <v>185.4506472</v>
       </c>
       <c r="N52">
-        <v>-80.73936000000002</v>
+        <v>-84.37564720000002</v>
       </c>
       <c r="O52">
-        <v>-19.3774464</v>
+        <v>-20.250155328</v>
       </c>
       <c r="P52">
-        <v>-61.36191360000002</v>
+        <v>-64.12549187200001</v>
       </c>
       <c r="Q52">
-        <v>14.43808639999998</v>
+        <v>11.67450812799999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.135882130890109</v>
+        <v>0.137720541724601</v>
       </c>
       <c r="T52">
-        <v>1.852183424186188</v>
+        <v>1.889983085904274</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1334218045263311</v>
+        <v>0.1308056907120894</v>
       </c>
       <c r="W52">
-        <v>0.1740089016511127</v>
+        <v>0.1745342173050125</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5559241855263797</v>
+        <v>0.5450237113003722</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1564955162706109</v>
+        <v>0.1580455162706109</v>
       </c>
       <c r="C53">
-        <v>-56.11606892048792</v>
+        <v>-82.93776921949575</v>
       </c>
       <c r="D53">
-        <v>630.9429310795122</v>
+        <v>622.2302307805044</v>
       </c>
       <c r="E53">
-        <v>351.6590000000001</v>
+        <v>369.7680000000001</v>
       </c>
       <c r="F53">
-        <v>923.5590000000001</v>
+        <v>941.6680000000001</v>
       </c>
       <c r="G53">
         <v>236.5</v>
@@ -5639,37 +5639,37 @@
         <v>101.075</v>
       </c>
       <c r="M53">
-        <v>185.4506472</v>
+        <v>189.0869344</v>
       </c>
       <c r="N53">
-        <v>-84.37564720000002</v>
+        <v>-88.01193440000002</v>
       </c>
       <c r="O53">
-        <v>-20.250155328</v>
+        <v>-21.122864256</v>
       </c>
       <c r="P53">
-        <v>-64.12549187200001</v>
+        <v>-66.88907014400002</v>
       </c>
       <c r="Q53">
-        <v>11.67450812799999</v>
+        <v>8.910929855999981</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.137720541724601</v>
+        <v>0.1396355530105302</v>
       </c>
       <c r="T53">
-        <v>1.889983085904274</v>
+        <v>1.92935773352728</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1308056907120894</v>
+        <v>0.1282901966599338</v>
       </c>
       <c r="W53">
-        <v>0.1745342173050125</v>
+        <v>0.1750393285106853</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5450237113003722</v>
+        <v>0.5345424860830574</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1580455162706109</v>
+        <v>0.1595955162706109</v>
       </c>
       <c r="C54">
-        <v>-82.93776921949575</v>
+        <v>-109.5221194733341</v>
       </c>
       <c r="D54">
-        <v>622.2302307805044</v>
+        <v>613.7548805266659</v>
       </c>
       <c r="E54">
-        <v>369.7680000000001</v>
+        <v>387.8770000000001</v>
       </c>
       <c r="F54">
-        <v>941.6680000000001</v>
+        <v>959.777</v>
       </c>
       <c r="G54">
         <v>236.5</v>
@@ -5721,37 +5721,37 @@
         <v>101.075</v>
       </c>
       <c r="M54">
-        <v>189.0869344</v>
+        <v>192.7232216</v>
       </c>
       <c r="N54">
-        <v>-88.01193440000002</v>
+        <v>-91.64822160000001</v>
       </c>
       <c r="O54">
-        <v>-21.122864256</v>
+        <v>-21.995573184</v>
       </c>
       <c r="P54">
-        <v>-66.88907014400002</v>
+        <v>-69.65264841600001</v>
       </c>
       <c r="Q54">
-        <v>8.910929855999981</v>
+        <v>6.147351583999992</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1396355530105302</v>
+        <v>0.1416320541384138</v>
       </c>
       <c r="T54">
-        <v>1.92935773352728</v>
+        <v>1.970407898070413</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1282901966599338</v>
+        <v>0.1258696269116331</v>
       </c>
       <c r="W54">
-        <v>0.1750393285106853</v>
+        <v>0.1755253789161441</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5345424860830574</v>
+        <v>0.5244567787984715</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1595955162706109</v>
+        <v>0.1611455162706109</v>
       </c>
       <c r="C55">
-        <v>-109.5221194733341</v>
+        <v>-135.8786881311781</v>
       </c>
       <c r="D55">
-        <v>613.7548805266659</v>
+        <v>605.5073118688219</v>
       </c>
       <c r="E55">
-        <v>387.8770000000001</v>
+        <v>405.9860000000001</v>
       </c>
       <c r="F55">
-        <v>959.777</v>
+        <v>977.8860000000001</v>
       </c>
       <c r="G55">
         <v>236.5</v>
@@ -5803,37 +5803,37 @@
         <v>101.075</v>
       </c>
       <c r="M55">
-        <v>192.7232216</v>
+        <v>196.3595088</v>
       </c>
       <c r="N55">
-        <v>-91.64822160000001</v>
+        <v>-95.28450880000001</v>
       </c>
       <c r="O55">
-        <v>-21.995573184</v>
+        <v>-22.868282112</v>
       </c>
       <c r="P55">
-        <v>-69.65264841600001</v>
+        <v>-72.41622668800001</v>
       </c>
       <c r="Q55">
-        <v>6.147351583999992</v>
+        <v>3.383773311999988</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1416320541384138</v>
+        <v>0.143715359663162</v>
       </c>
       <c r="T55">
-        <v>1.970407898070413</v>
+        <v>2.013242852376291</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1258696269116331</v>
+        <v>0.123538707894751</v>
       </c>
       <c r="W55">
-        <v>0.1755253789161441</v>
+        <v>0.175993427454734</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5244567787984715</v>
+        <v>0.5147446162281294</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1611455162706109</v>
+        <v>0.1626955162706109</v>
       </c>
       <c r="C56">
-        <v>-135.8786881311781</v>
+        <v>-162.0165361429699</v>
       </c>
       <c r="D56">
-        <v>605.5073118688219</v>
+        <v>597.4784638570302</v>
       </c>
       <c r="E56">
-        <v>405.9860000000001</v>
+        <v>424.0950000000001</v>
       </c>
       <c r="F56">
-        <v>977.8860000000001</v>
+        <v>995.9950000000001</v>
       </c>
       <c r="G56">
         <v>236.5</v>
@@ -5885,37 +5885,37 @@
         <v>101.075</v>
       </c>
       <c r="M56">
-        <v>196.3595088</v>
+        <v>199.995796</v>
       </c>
       <c r="N56">
-        <v>-95.28450880000001</v>
+        <v>-98.92079600000004</v>
       </c>
       <c r="O56">
-        <v>-22.868282112</v>
+        <v>-23.74099104000001</v>
       </c>
       <c r="P56">
-        <v>-72.41622668800001</v>
+        <v>-75.17980496000003</v>
       </c>
       <c r="Q56">
-        <v>3.383773311999988</v>
+        <v>0.6201950399999703</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.143715359663162</v>
+        <v>0.1458912565445656</v>
       </c>
       <c r="T56">
-        <v>2.013242852376291</v>
+        <v>2.057981582429098</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.123538707894751</v>
+        <v>0.1212925495693919</v>
       </c>
       <c r="W56">
-        <v>0.175993427454734</v>
+        <v>0.1764444560464661</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5147446162281294</v>
+        <v>0.5053856232057997</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1626955162706109</v>
+        <v>0.1843233904009408</v>
       </c>
       <c r="C57">
-        <v>-162.0165361429699</v>
+        <v>-273.4107854750929</v>
       </c>
       <c r="D57">
-        <v>597.4784638570302</v>
+        <v>504.1932145249073</v>
       </c>
       <c r="E57">
-        <v>424.0950000000001</v>
+        <v>442.2040000000002</v>
       </c>
       <c r="F57">
-        <v>995.9950000000001</v>
+        <v>1014.104</v>
       </c>
       <c r="G57">
         <v>236.5</v>
@@ -5967,45 +5967,45 @@
         <v>101.075</v>
       </c>
       <c r="M57">
-        <v>199.995796</v>
+        <v>239.1257232</v>
       </c>
       <c r="N57">
-        <v>-98.92079600000004</v>
+        <v>-138.0507232</v>
       </c>
       <c r="O57">
-        <v>-23.74099104000001</v>
+        <v>-33.13217356800001</v>
       </c>
       <c r="P57">
-        <v>-75.17980496000003</v>
+        <v>-104.918549632</v>
       </c>
       <c r="Q57">
-        <v>0.6201950399999703</v>
+        <v>-29.11854963200004</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1458912565445656</v>
+        <v>0.149252135398601</v>
       </c>
       <c r="T57">
-        <v>2.057981582429098</v>
+        <v>2.127084789054352</v>
       </c>
       <c r="U57">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1212925495693919</v>
+        <v>0.1014445442145556</v>
       </c>
       <c r="W57">
-        <v>0.1764444560464661</v>
+        <v>0.2118793764742078</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.5053856232057997</v>
+        <v>0.4226856008939819</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1843233904009408</v>
+        <v>0.1862233904009408</v>
       </c>
       <c r="C58">
-        <v>-273.4107854750929</v>
+        <v>-298.341776489995</v>
       </c>
       <c r="D58">
-        <v>504.1932145249073</v>
+        <v>497.3712235100052</v>
       </c>
       <c r="E58">
-        <v>442.2040000000002</v>
+        <v>460.3130000000002</v>
       </c>
       <c r="F58">
-        <v>1014.104</v>
+        <v>1032.213</v>
       </c>
       <c r="G58">
         <v>236.5</v>
@@ -6049,37 +6049,37 @@
         <v>101.075</v>
       </c>
       <c r="M58">
-        <v>239.1257232</v>
+        <v>243.3958254000001</v>
       </c>
       <c r="N58">
-        <v>-138.0507232</v>
+        <v>-142.3208254</v>
       </c>
       <c r="O58">
-        <v>-33.13217356800001</v>
+        <v>-34.15699809600001</v>
       </c>
       <c r="P58">
-        <v>-104.918549632</v>
+        <v>-108.163827304</v>
       </c>
       <c r="Q58">
-        <v>-29.11854963200004</v>
+        <v>-32.36382730400004</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.149252135398601</v>
+        <v>0.151657999012522</v>
       </c>
       <c r="T58">
-        <v>2.127084789054352</v>
+        <v>2.176551877171895</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1014445442145556</v>
+        <v>0.09966481536868625</v>
       </c>
       <c r="W58">
-        <v>0.2118793764742078</v>
+        <v>0.2122990365360638</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4226856008939819</v>
+        <v>0.4152700640361927</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1862233904009408</v>
+        <v>0.1881233904009408</v>
       </c>
       <c r="C59">
-        <v>-298.341776489995</v>
+        <v>-323.0906219996251</v>
       </c>
       <c r="D59">
-        <v>497.3712235100052</v>
+        <v>490.731378000375</v>
       </c>
       <c r="E59">
-        <v>460.3130000000002</v>
+        <v>478.4220000000001</v>
       </c>
       <c r="F59">
-        <v>1032.213</v>
+        <v>1050.322</v>
       </c>
       <c r="G59">
         <v>236.5</v>
@@ -6131,37 +6131,37 @@
         <v>101.075</v>
       </c>
       <c r="M59">
-        <v>243.3958254000001</v>
+        <v>247.6659276</v>
       </c>
       <c r="N59">
-        <v>-142.3208254</v>
+        <v>-146.5909276</v>
       </c>
       <c r="O59">
-        <v>-34.15699809600001</v>
+        <v>-35.18182262400001</v>
       </c>
       <c r="P59">
-        <v>-108.163827304</v>
+        <v>-111.409104976</v>
       </c>
       <c r="Q59">
-        <v>-32.36382730400004</v>
+        <v>-35.60910497600004</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.151657999012522</v>
+        <v>0.1541784275604392</v>
       </c>
       <c r="T59">
-        <v>2.176551877171895</v>
+        <v>2.228374540914083</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.09966481536868625</v>
+        <v>0.09794645648301925</v>
       </c>
       <c r="W59">
-        <v>0.2122990365360638</v>
+        <v>0.2127042255613041</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4152700640361927</v>
+        <v>0.4081102353459135</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1881233904009408</v>
+        <v>0.1900233904009408</v>
       </c>
       <c r="C60">
-        <v>-323.0906219996249</v>
+        <v>-347.6645207626389</v>
       </c>
       <c r="D60">
-        <v>490.731378000375</v>
+        <v>484.2664792373612</v>
       </c>
       <c r="E60">
-        <v>478.4219999999999</v>
+        <v>496.5310000000001</v>
       </c>
       <c r="F60">
-        <v>1050.322</v>
+        <v>1068.431</v>
       </c>
       <c r="G60">
         <v>236.5</v>
@@ -6213,37 +6213,37 @@
         <v>101.075</v>
       </c>
       <c r="M60">
-        <v>247.6659276</v>
+        <v>251.9360298</v>
       </c>
       <c r="N60">
-        <v>-146.5909276</v>
+        <v>-150.8610298</v>
       </c>
       <c r="O60">
-        <v>-35.181822624</v>
+        <v>-36.20664715200001</v>
       </c>
       <c r="P60">
-        <v>-111.409104976</v>
+        <v>-114.654382648</v>
       </c>
       <c r="Q60">
-        <v>-35.60910497599998</v>
+        <v>-38.85438264800003</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1541784275604392</v>
+        <v>0.1568218038424011</v>
       </c>
       <c r="T60">
-        <v>2.228374540914083</v>
+        <v>2.282725139472963</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.09794645648301928</v>
+        <v>0.09628634705110369</v>
       </c>
       <c r="W60">
-        <v>0.2127042255613041</v>
+        <v>0.2130956793653498</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4081102353459136</v>
+        <v>0.4011931127129319</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1900233904009408</v>
+        <v>0.1919233904009408</v>
       </c>
       <c r="C61">
-        <v>-347.6645207626389</v>
+        <v>-372.0702971242216</v>
       </c>
       <c r="D61">
-        <v>484.2664792373612</v>
+        <v>477.9697028757784</v>
       </c>
       <c r="E61">
-        <v>496.5310000000001</v>
+        <v>514.64</v>
       </c>
       <c r="F61">
-        <v>1068.431</v>
+        <v>1086.54</v>
       </c>
       <c r="G61">
         <v>236.5</v>
@@ -6295,37 +6295,37 @@
         <v>101.075</v>
       </c>
       <c r="M61">
-        <v>251.9360298</v>
+        <v>256.206132</v>
       </c>
       <c r="N61">
-        <v>-150.8610298</v>
+        <v>-155.131132</v>
       </c>
       <c r="O61">
-        <v>-36.20664715200001</v>
+        <v>-37.23147168000001</v>
       </c>
       <c r="P61">
-        <v>-114.654382648</v>
+        <v>-117.89966032</v>
       </c>
       <c r="Q61">
-        <v>-38.85438264800003</v>
+        <v>-42.09966032000004</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1568218038424011</v>
+        <v>0.1595973489384611</v>
       </c>
       <c r="T61">
-        <v>2.282725139472963</v>
+        <v>2.339793267959787</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.09628634705110369</v>
+        <v>0.09468157460025195</v>
       </c>
       <c r="W61">
-        <v>0.2130956793653498</v>
+        <v>0.2134740847092606</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4011931127129319</v>
+        <v>0.3945065608343831</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1919233904009408</v>
+        <v>0.1938233904009408</v>
       </c>
       <c r="C62">
-        <v>-372.0702971242216</v>
+        <v>-396.3144250455871</v>
       </c>
       <c r="D62">
-        <v>477.9697028757784</v>
+        <v>471.8345749544131</v>
       </c>
       <c r="E62">
-        <v>514.64</v>
+        <v>532.7490000000001</v>
       </c>
       <c r="F62">
-        <v>1086.54</v>
+        <v>1104.649</v>
       </c>
       <c r="G62">
         <v>236.5</v>
@@ -6377,37 +6377,37 @@
         <v>101.075</v>
       </c>
       <c r="M62">
-        <v>256.206132</v>
+        <v>260.4762342</v>
       </c>
       <c r="N62">
-        <v>-155.131132</v>
+        <v>-159.4012342</v>
       </c>
       <c r="O62">
-        <v>-37.23147168000001</v>
+        <v>-38.25629620800001</v>
       </c>
       <c r="P62">
-        <v>-117.89966032</v>
+        <v>-121.144937992</v>
       </c>
       <c r="Q62">
-        <v>-42.09966032000004</v>
+        <v>-45.34493799200003</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1595973489384611</v>
+        <v>0.162515229680473</v>
       </c>
       <c r="T62">
-        <v>2.339793267959787</v>
+        <v>2.399787967138244</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.09468157460025195</v>
+        <v>0.09312941763959208</v>
       </c>
       <c r="W62">
-        <v>0.2134740847092606</v>
+        <v>0.2138400833205842</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3945065608343831</v>
+        <v>0.3880392401649669</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1938233904009408</v>
+        <v>0.1957233904009408</v>
       </c>
       <c r="C63">
-        <v>-396.3144250455871</v>
+        <v>-420.4030503063012</v>
       </c>
       <c r="D63">
-        <v>471.8345749544131</v>
+        <v>465.8549496936988</v>
       </c>
       <c r="E63">
-        <v>532.7490000000001</v>
+        <v>550.8580000000001</v>
       </c>
       <c r="F63">
-        <v>1104.649</v>
+        <v>1122.758</v>
       </c>
       <c r="G63">
         <v>236.5</v>
@@ -6459,37 +6459,37 @@
         <v>101.075</v>
       </c>
       <c r="M63">
-        <v>260.4762342</v>
+        <v>264.7463364</v>
       </c>
       <c r="N63">
-        <v>-159.4012342</v>
+        <v>-163.6713364</v>
       </c>
       <c r="O63">
-        <v>-38.25629620800001</v>
+        <v>-39.28112073600001</v>
       </c>
       <c r="P63">
-        <v>-121.144937992</v>
+        <v>-124.390215664</v>
       </c>
       <c r="Q63">
-        <v>-45.34493799200003</v>
+        <v>-48.59021566400003</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.162515229680473</v>
+        <v>0.165586683093117</v>
       </c>
       <c r="T63">
-        <v>2.399787967138244</v>
+        <v>2.462940282062934</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.09312941763959208</v>
+        <v>0.09162733025830834</v>
       </c>
       <c r="W63">
-        <v>0.2138400833205842</v>
+        <v>0.2141942755250909</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3880392401649669</v>
+        <v>0.3817805427429514</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1957233904009408</v>
+        <v>0.1976233904009408</v>
       </c>
       <c r="C64">
-        <v>-420.4030503063012</v>
+        <v>-444.3420110394961</v>
       </c>
       <c r="D64">
-        <v>465.8549496936988</v>
+        <v>460.0249889605038</v>
       </c>
       <c r="E64">
-        <v>550.8580000000001</v>
+        <v>568.967</v>
       </c>
       <c r="F64">
-        <v>1122.758</v>
+        <v>1140.867</v>
       </c>
       <c r="G64">
         <v>236.5</v>
@@ -6541,37 +6541,37 @@
         <v>101.075</v>
       </c>
       <c r="M64">
-        <v>264.7463364</v>
+        <v>269.0164386</v>
       </c>
       <c r="N64">
-        <v>-163.6713364</v>
+        <v>-167.9414386</v>
       </c>
       <c r="O64">
-        <v>-39.28112073600001</v>
+        <v>-40.305945264</v>
       </c>
       <c r="P64">
-        <v>-124.390215664</v>
+        <v>-127.635493336</v>
       </c>
       <c r="Q64">
-        <v>-48.59021566400003</v>
+        <v>-51.83549333600003</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.165586683093117</v>
+        <v>0.1688241610145526</v>
       </c>
       <c r="T64">
-        <v>2.462940282062934</v>
+        <v>2.529506235632202</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.09162733025830834</v>
+        <v>0.09017292819071615</v>
       </c>
       <c r="W64">
-        <v>0.2141942755250909</v>
+        <v>0.2145372235326291</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3817805427429514</v>
+        <v>0.3757205341279839</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1976233904009408</v>
+        <v>0.1995233904009408</v>
       </c>
       <c r="C65">
-        <v>-444.3420110394961</v>
+        <v>-468.1368567442084</v>
       </c>
       <c r="D65">
-        <v>460.0249889605038</v>
+        <v>454.3391432557916</v>
       </c>
       <c r="E65">
-        <v>568.967</v>
+        <v>587.0760000000001</v>
       </c>
       <c r="F65">
-        <v>1140.867</v>
+        <v>1158.976</v>
       </c>
       <c r="G65">
         <v>236.5</v>
@@ -6623,37 +6623,37 @@
         <v>101.075</v>
       </c>
       <c r="M65">
-        <v>269.0164386</v>
+        <v>273.2865408</v>
       </c>
       <c r="N65">
-        <v>-167.9414386</v>
+        <v>-172.2115408</v>
       </c>
       <c r="O65">
-        <v>-40.305945264</v>
+        <v>-41.33076979200001</v>
       </c>
       <c r="P65">
-        <v>-127.635493336</v>
+        <v>-130.880771008</v>
       </c>
       <c r="Q65">
-        <v>-51.83549333600003</v>
+        <v>-55.08077100800001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1688241610145526</v>
+        <v>0.1722414988205124</v>
       </c>
       <c r="T65">
-        <v>2.529506235632202</v>
+        <v>2.599770297733097</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.09017292819071615</v>
+        <v>0.0887639761877362</v>
       </c>
       <c r="W65">
-        <v>0.2145372235326291</v>
+        <v>0.2148694544149318</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3757205341279839</v>
+        <v>0.3698499007822341</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1995233904009408</v>
+        <v>0.2014233904009409</v>
       </c>
       <c r="C66">
-        <v>-468.1368567442084</v>
+        <v>-491.7928659049907</v>
       </c>
       <c r="D66">
-        <v>454.3391432557916</v>
+        <v>448.7921340950094</v>
       </c>
       <c r="E66">
-        <v>587.0760000000001</v>
+        <v>605.1850000000001</v>
       </c>
       <c r="F66">
-        <v>1158.976</v>
+        <v>1177.085</v>
       </c>
       <c r="G66">
         <v>236.5</v>
@@ -6705,37 +6705,37 @@
         <v>101.075</v>
       </c>
       <c r="M66">
-        <v>273.2865408</v>
+        <v>277.556643</v>
       </c>
       <c r="N66">
-        <v>-172.2115408</v>
+        <v>-176.481643</v>
       </c>
       <c r="O66">
-        <v>-41.33076979200001</v>
+        <v>-42.35559432</v>
       </c>
       <c r="P66">
-        <v>-130.880771008</v>
+        <v>-134.12604868</v>
       </c>
       <c r="Q66">
-        <v>-55.08077100800001</v>
+        <v>-58.32604868000003</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1722414988205124</v>
+        <v>0.1758541130725271</v>
       </c>
       <c r="T66">
-        <v>2.599770297733097</v>
+        <v>2.6740494490969</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0887639761877362</v>
+        <v>0.08739837655407873</v>
       </c>
       <c r="W66">
-        <v>0.2148694544149318</v>
+        <v>0.2151914628085483</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3698499007822341</v>
+        <v>0.3641599023086614</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2014233904009409</v>
+        <v>0.2033233904009408</v>
       </c>
       <c r="C67">
-        <v>-491.7928659049907</v>
+        <v>-515.3150623363913</v>
       </c>
       <c r="D67">
-        <v>448.7921340950094</v>
+        <v>443.3789376636088</v>
       </c>
       <c r="E67">
-        <v>605.1850000000001</v>
+        <v>623.2940000000002</v>
       </c>
       <c r="F67">
-        <v>1177.085</v>
+        <v>1195.194</v>
       </c>
       <c r="G67">
         <v>236.5</v>
@@ -6787,37 +6787,37 @@
         <v>101.075</v>
       </c>
       <c r="M67">
-        <v>277.556643</v>
+        <v>281.8267452000001</v>
       </c>
       <c r="N67">
-        <v>-176.481643</v>
+        <v>-180.7517452000001</v>
       </c>
       <c r="O67">
-        <v>-42.35559432</v>
+        <v>-43.38041884800002</v>
       </c>
       <c r="P67">
-        <v>-134.12604868</v>
+        <v>-137.371326352</v>
       </c>
       <c r="Q67">
-        <v>-58.32604868000003</v>
+        <v>-61.57132635200004</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1758541130725271</v>
+        <v>0.1796792340452484</v>
       </c>
       <c r="T67">
-        <v>2.6740494490969</v>
+        <v>2.752697962305632</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08739837655407873</v>
+        <v>0.08607415872750176</v>
       </c>
       <c r="W67">
-        <v>0.2151914628085483</v>
+        <v>0.2155037133720551</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3641599023086614</v>
+        <v>0.3586423280312573</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2033233904009408</v>
+        <v>0.2052233904009408</v>
       </c>
       <c r="C68">
-        <v>-515.3150623363913</v>
+        <v>-538.708230358676</v>
       </c>
       <c r="D68">
-        <v>443.3789376636088</v>
+        <v>438.0947696413241</v>
       </c>
       <c r="E68">
-        <v>623.2940000000002</v>
+        <v>641.4030000000001</v>
       </c>
       <c r="F68">
-        <v>1195.194</v>
+        <v>1213.303</v>
       </c>
       <c r="G68">
         <v>236.5</v>
@@ -6869,37 +6869,37 @@
         <v>101.075</v>
       </c>
       <c r="M68">
-        <v>281.8267452000001</v>
+        <v>286.0968474000001</v>
       </c>
       <c r="N68">
-        <v>-180.7517452000001</v>
+        <v>-185.0218474000001</v>
       </c>
       <c r="O68">
-        <v>-43.38041884800002</v>
+        <v>-44.40524337600002</v>
       </c>
       <c r="P68">
-        <v>-137.371326352</v>
+        <v>-140.6166040240001</v>
       </c>
       <c r="Q68">
-        <v>-61.57132635200004</v>
+        <v>-64.81660402400006</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1796792340452484</v>
+        <v>0.1837361805314681</v>
       </c>
       <c r="T68">
-        <v>2.752697962305632</v>
+        <v>2.83611305207247</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08607415872750176</v>
+        <v>0.0847894697912704</v>
       </c>
       <c r="W68">
-        <v>0.2155037133720551</v>
+        <v>0.2158066430232184</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3586423280312573</v>
+        <v>0.3532894574636266</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2052233904009408</v>
+        <v>0.2071233904009409</v>
       </c>
       <c r="C69">
-        <v>-538.708230358676</v>
+        <v>-561.976928901149</v>
       </c>
       <c r="D69">
-        <v>438.0947696413241</v>
+        <v>432.9350710988513</v>
       </c>
       <c r="E69">
-        <v>641.4030000000001</v>
+        <v>659.5120000000003</v>
       </c>
       <c r="F69">
-        <v>1213.303</v>
+        <v>1231.412</v>
       </c>
       <c r="G69">
         <v>236.5</v>
@@ -6951,37 +6951,37 @@
         <v>101.075</v>
       </c>
       <c r="M69">
-        <v>286.0968474000001</v>
+        <v>290.3669496000001</v>
       </c>
       <c r="N69">
-        <v>-185.0218474000001</v>
+        <v>-189.2919496000001</v>
       </c>
       <c r="O69">
-        <v>-44.40524337600002</v>
+        <v>-45.43006790400001</v>
       </c>
       <c r="P69">
-        <v>-140.6166040240001</v>
+        <v>-143.8618816960001</v>
       </c>
       <c r="Q69">
-        <v>-64.81660402400006</v>
+        <v>-68.06188169600007</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1837361805314681</v>
+        <v>0.1880466861730765</v>
       </c>
       <c r="T69">
-        <v>2.83611305207247</v>
+        <v>2.924741584949734</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0847894697912704</v>
+        <v>0.0835425658237517</v>
       </c>
       <c r="W69">
-        <v>0.2158066430232184</v>
+        <v>0.2161006629787594</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3532894574636266</v>
+        <v>0.3480940242656321</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2071233904009409</v>
+        <v>0.2090233904009408</v>
       </c>
       <c r="C70">
-        <v>-561.976928901149</v>
+        <v>-585.1255046204577</v>
       </c>
       <c r="D70">
-        <v>432.9350710988513</v>
+        <v>427.8954953795425</v>
       </c>
       <c r="E70">
-        <v>659.5120000000003</v>
+        <v>677.6210000000002</v>
       </c>
       <c r="F70">
-        <v>1231.412</v>
+        <v>1249.521</v>
       </c>
       <c r="G70">
         <v>236.5</v>
@@ -7033,37 +7033,37 @@
         <v>101.075</v>
       </c>
       <c r="M70">
-        <v>290.3669496000001</v>
+        <v>294.6370518000001</v>
       </c>
       <c r="N70">
-        <v>-189.2919496000001</v>
+        <v>-193.5620518000001</v>
       </c>
       <c r="O70">
-        <v>-45.43006790400001</v>
+        <v>-46.45489243200002</v>
       </c>
       <c r="P70">
-        <v>-143.8618816960001</v>
+        <v>-147.1071593680001</v>
       </c>
       <c r="Q70">
-        <v>-68.06188169600007</v>
+        <v>-71.30715936800006</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1880466861730765</v>
+        <v>0.1926352889528531</v>
       </c>
       <c r="T70">
-        <v>2.924741584949734</v>
+        <v>3.019088087690049</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0835425658237517</v>
+        <v>0.08233180400021908</v>
       </c>
       <c r="W70">
-        <v>0.2161006629787594</v>
+        <v>0.2163861606167483</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3480940242656321</v>
+        <v>0.3430491833342462</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2090233904009408</v>
+        <v>0.2109233904009409</v>
       </c>
       <c r="C71">
-        <v>-585.1255046204577</v>
+        <v>-608.1581041132191</v>
       </c>
       <c r="D71">
-        <v>427.8954953795425</v>
+        <v>422.971895886781</v>
       </c>
       <c r="E71">
-        <v>677.6210000000002</v>
+        <v>695.7300000000001</v>
       </c>
       <c r="F71">
-        <v>1249.521</v>
+        <v>1267.63</v>
       </c>
       <c r="G71">
         <v>236.5</v>
@@ -7115,37 +7115,37 @@
         <v>101.075</v>
       </c>
       <c r="M71">
-        <v>294.6370518000001</v>
+        <v>298.907154</v>
       </c>
       <c r="N71">
-        <v>-193.5620518000001</v>
+        <v>-197.8321540000001</v>
       </c>
       <c r="O71">
-        <v>-46.45489243200002</v>
+        <v>-47.47971696000001</v>
       </c>
       <c r="P71">
-        <v>-147.1071593680001</v>
+        <v>-150.35243704</v>
       </c>
       <c r="Q71">
-        <v>-71.30715936800006</v>
+        <v>-74.55243704000004</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1926352889528531</v>
+        <v>0.1975297985846149</v>
       </c>
       <c r="T71">
-        <v>3.019088087690049</v>
+        <v>3.119724357279717</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08233180400021908</v>
+        <v>0.08115563537164451</v>
       </c>
       <c r="W71">
-        <v>0.2163861606167483</v>
+        <v>0.2166635011793662</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3430491833342462</v>
+        <v>0.3381484807151854</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2109233904009409</v>
+        <v>0.2128233904009408</v>
       </c>
       <c r="C72">
-        <v>-608.1581041132191</v>
+        <v>-631.0786852950866</v>
       </c>
       <c r="D72">
-        <v>422.971895886781</v>
+        <v>418.1603147049136</v>
       </c>
       <c r="E72">
-        <v>695.7300000000001</v>
+        <v>713.8390000000003</v>
       </c>
       <c r="F72">
-        <v>1267.63</v>
+        <v>1285.739</v>
       </c>
       <c r="G72">
         <v>236.5</v>
@@ -7197,37 +7197,37 @@
         <v>101.075</v>
       </c>
       <c r="M72">
-        <v>298.907154</v>
+        <v>303.1772562000001</v>
       </c>
       <c r="N72">
-        <v>-197.8321540000001</v>
+        <v>-202.1022562000001</v>
       </c>
       <c r="O72">
-        <v>-47.47971696000001</v>
+        <v>-48.50454148800002</v>
       </c>
       <c r="P72">
-        <v>-150.35243704</v>
+        <v>-153.5977147120001</v>
       </c>
       <c r="Q72">
-        <v>-74.55243704000004</v>
+        <v>-77.79771471200009</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1975297985846149</v>
+        <v>0.2027618606047741</v>
       </c>
       <c r="T72">
-        <v>3.119724357279717</v>
+        <v>3.22730105925488</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08115563537164451</v>
+        <v>0.08001259825373402</v>
       </c>
       <c r="W72">
-        <v>0.2166635011793662</v>
+        <v>0.2169330293317695</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3381484807151854</v>
+        <v>0.333385826057225</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2128233904009408</v>
+        <v>0.2147233904009408</v>
       </c>
       <c r="C73">
-        <v>-631.0786852950866</v>
+        <v>-653.891028011886</v>
       </c>
       <c r="D73">
-        <v>418.1603147049134</v>
+        <v>413.456971988114</v>
       </c>
       <c r="E73">
-        <v>713.8390000000001</v>
+        <v>731.948</v>
       </c>
       <c r="F73">
-        <v>1285.739</v>
+        <v>1303.848</v>
       </c>
       <c r="G73">
         <v>236.5</v>
@@ -7279,37 +7279,37 @@
         <v>101.075</v>
       </c>
       <c r="M73">
-        <v>303.1772562</v>
+        <v>307.4473584</v>
       </c>
       <c r="N73">
-        <v>-202.1022562000001</v>
+        <v>-206.3723584</v>
       </c>
       <c r="O73">
-        <v>-48.50454148800002</v>
+        <v>-49.529366016</v>
       </c>
       <c r="P73">
-        <v>-153.597714712</v>
+        <v>-156.842992384</v>
       </c>
       <c r="Q73">
-        <v>-77.79771471200003</v>
+        <v>-81.04299238400002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.202761860604774</v>
+        <v>0.2083676413406588</v>
       </c>
       <c r="T73">
-        <v>3.227301059254879</v>
+        <v>3.342561811371124</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08001259825373404</v>
+        <v>0.07890131216687662</v>
       </c>
       <c r="W73">
-        <v>0.2169330293317695</v>
+        <v>0.2171950705910505</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3333858260572251</v>
+        <v>0.3287554673619859</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2147233904009408</v>
+        <v>0.2166233904009408</v>
       </c>
       <c r="C74">
-        <v>-653.891028011886</v>
+        <v>-676.5987439426119</v>
       </c>
       <c r="D74">
-        <v>413.456971988114</v>
+        <v>408.8582560573882</v>
       </c>
       <c r="E74">
-        <v>731.948</v>
+        <v>750.0570000000001</v>
       </c>
       <c r="F74">
-        <v>1303.848</v>
+        <v>1321.957</v>
       </c>
       <c r="G74">
         <v>236.5</v>
@@ -7361,37 +7361,37 @@
         <v>101.075</v>
       </c>
       <c r="M74">
-        <v>307.4473584</v>
+        <v>311.7174606</v>
       </c>
       <c r="N74">
-        <v>-206.3723584</v>
+        <v>-210.6424606</v>
       </c>
       <c r="O74">
-        <v>-49.529366016</v>
+        <v>-50.55419054400001</v>
       </c>
       <c r="P74">
-        <v>-156.842992384</v>
+        <v>-160.0882700560001</v>
       </c>
       <c r="Q74">
-        <v>-81.04299238400002</v>
+        <v>-84.28827005600006</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2083676413406588</v>
+        <v>0.2143886650940165</v>
       </c>
       <c r="T74">
-        <v>3.342561811371124</v>
+        <v>3.466360396977462</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07890131216687662</v>
+        <v>0.07782047227417968</v>
       </c>
       <c r="W74">
-        <v>0.2171950705910505</v>
+        <v>0.2174499326377484</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3287554673619859</v>
+        <v>0.3242519678090819</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2166233904009408</v>
+        <v>0.2185233904009408</v>
       </c>
       <c r="C75">
-        <v>-676.5987439426119</v>
+        <v>-699.2052858488112</v>
       </c>
       <c r="D75">
-        <v>408.8582560573882</v>
+        <v>404.3607141511889</v>
       </c>
       <c r="E75">
-        <v>750.0570000000001</v>
+        <v>768.1660000000001</v>
       </c>
       <c r="F75">
-        <v>1321.957</v>
+        <v>1340.066</v>
       </c>
       <c r="G75">
         <v>236.5</v>
@@ -7443,37 +7443,37 @@
         <v>101.075</v>
       </c>
       <c r="M75">
-        <v>311.7174606</v>
+        <v>315.9875628</v>
       </c>
       <c r="N75">
-        <v>-210.6424606</v>
+        <v>-214.9125628</v>
       </c>
       <c r="O75">
-        <v>-50.55419054400001</v>
+        <v>-51.57901507200001</v>
       </c>
       <c r="P75">
-        <v>-160.0882700560001</v>
+        <v>-163.333547728</v>
       </c>
       <c r="Q75">
-        <v>-84.28827005600006</v>
+        <v>-87.53354772800004</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2143886650940165</v>
+        <v>0.2208728445207095</v>
       </c>
       <c r="T75">
-        <v>3.466360396977462</v>
+        <v>3.599681950707365</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07782047227417968</v>
+        <v>0.07676884427047455</v>
       </c>
       <c r="W75">
-        <v>0.2174499326377484</v>
+        <v>0.2176979065210221</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3242519678090819</v>
+        <v>0.3198701844603106</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2185233904009408</v>
+        <v>0.2204233904009408</v>
       </c>
       <c r="C76">
-        <v>-699.2052858488112</v>
+        <v>-721.7139562201357</v>
       </c>
       <c r="D76">
-        <v>404.3607141511889</v>
+        <v>399.9610437798644</v>
       </c>
       <c r="E76">
-        <v>768.1660000000001</v>
+        <v>786.2750000000002</v>
       </c>
       <c r="F76">
-        <v>1340.066</v>
+        <v>1358.175</v>
       </c>
       <c r="G76">
         <v>236.5</v>
@@ -7525,37 +7525,37 @@
         <v>101.075</v>
       </c>
       <c r="M76">
-        <v>315.9875628</v>
+        <v>320.257665</v>
       </c>
       <c r="N76">
-        <v>-214.9125628</v>
+        <v>-219.182665</v>
       </c>
       <c r="O76">
-        <v>-51.57901507200001</v>
+        <v>-52.60383960000001</v>
       </c>
       <c r="P76">
-        <v>-163.333547728</v>
+        <v>-166.5788254</v>
       </c>
       <c r="Q76">
-        <v>-87.53354772800004</v>
+        <v>-90.77882540000003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2208728445207095</v>
+        <v>0.2278757583015379</v>
       </c>
       <c r="T76">
-        <v>3.599681950707365</v>
+        <v>3.743669228735659</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07676884427047455</v>
+        <v>0.07574525968020156</v>
       </c>
       <c r="W76">
-        <v>0.2176979065210221</v>
+        <v>0.2179392677674085</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3198701844603106</v>
+        <v>0.3156052486675065</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2204233904009408</v>
+        <v>0.2223233904009408</v>
       </c>
       <c r="C77">
-        <v>-721.7139562201357</v>
+        <v>-744.1279153615601</v>
       </c>
       <c r="D77">
-        <v>399.9610437798644</v>
+        <v>395.6560846384399</v>
       </c>
       <c r="E77">
-        <v>786.2750000000002</v>
+        <v>804.3840000000001</v>
       </c>
       <c r="F77">
-        <v>1358.175</v>
+        <v>1376.284</v>
       </c>
       <c r="G77">
         <v>236.5</v>
@@ -7607,37 +7607,37 @@
         <v>101.075</v>
       </c>
       <c r="M77">
-        <v>320.257665</v>
+        <v>324.5277672</v>
       </c>
       <c r="N77">
-        <v>-219.182665</v>
+        <v>-223.4527672</v>
       </c>
       <c r="O77">
-        <v>-52.60383960000001</v>
+        <v>-53.628664128</v>
       </c>
       <c r="P77">
-        <v>-166.5788254</v>
+        <v>-169.824103072</v>
       </c>
       <c r="Q77">
-        <v>-90.77882540000003</v>
+        <v>-94.02410307200005</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2278757583015379</v>
+        <v>0.2354622482307686</v>
       </c>
       <c r="T77">
-        <v>3.743669228735659</v>
+        <v>3.899655446599646</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07574525968020156</v>
+        <v>0.07474861152651469</v>
       </c>
       <c r="W77">
-        <v>0.2179392677674085</v>
+        <v>0.2181742774020478</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3156052486675065</v>
+        <v>0.3114525480271445</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2223233904009408</v>
+        <v>0.2242233904009408</v>
       </c>
       <c r="C78">
-        <v>-744.1279153615601</v>
+        <v>-766.4501889638816</v>
       </c>
       <c r="D78">
-        <v>395.6560846384399</v>
+        <v>391.4428110361184</v>
       </c>
       <c r="E78">
-        <v>804.3840000000001</v>
+        <v>822.4930000000001</v>
       </c>
       <c r="F78">
-        <v>1376.284</v>
+        <v>1394.393</v>
       </c>
       <c r="G78">
         <v>236.5</v>
@@ -7689,37 +7689,37 @@
         <v>101.075</v>
       </c>
       <c r="M78">
-        <v>324.5277672</v>
+        <v>328.7978694</v>
       </c>
       <c r="N78">
-        <v>-223.4527672</v>
+        <v>-227.7228694</v>
       </c>
       <c r="O78">
-        <v>-53.628664128</v>
+        <v>-54.65348865600001</v>
       </c>
       <c r="P78">
-        <v>-169.824103072</v>
+        <v>-173.069380744</v>
       </c>
       <c r="Q78">
-        <v>-94.02410307200005</v>
+        <v>-97.26938074400003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2354622482307686</v>
+        <v>0.2437084329364542</v>
       </c>
       <c r="T78">
-        <v>3.899655446599646</v>
+        <v>4.069205683408326</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07474861152651469</v>
+        <v>0.07377785033785866</v>
       </c>
       <c r="W78">
-        <v>0.2181742774020478</v>
+        <v>0.2184031828903329</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3114525480271445</v>
+        <v>0.3074077097410777</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2242233904009408</v>
+        <v>0.2261233904009408</v>
       </c>
       <c r="C79">
-        <v>-766.4501889638816</v>
+        <v>-788.6836751956178</v>
       </c>
       <c r="D79">
-        <v>391.4428110361184</v>
+        <v>387.3183248043824</v>
       </c>
       <c r="E79">
-        <v>822.4930000000001</v>
+        <v>840.6020000000002</v>
       </c>
       <c r="F79">
-        <v>1394.393</v>
+        <v>1412.502</v>
       </c>
       <c r="G79">
         <v>236.5</v>
@@ -7771,37 +7771,37 @@
         <v>101.075</v>
       </c>
       <c r="M79">
-        <v>328.7978694</v>
+        <v>333.0679716000001</v>
       </c>
       <c r="N79">
-        <v>-227.7228694</v>
+        <v>-231.9929716000001</v>
       </c>
       <c r="O79">
-        <v>-54.65348865600001</v>
+        <v>-55.67831318400002</v>
       </c>
       <c r="P79">
-        <v>-173.069380744</v>
+        <v>-176.3146584160001</v>
       </c>
       <c r="Q79">
-        <v>-97.26938074400003</v>
+        <v>-100.5146584160001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2437084329364542</v>
+        <v>0.2527042707972021</v>
       </c>
       <c r="T79">
-        <v>4.069205683408326</v>
+        <v>4.254169578108704</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07377785033785866</v>
+        <v>0.07283198046173225</v>
       </c>
       <c r="W79">
-        <v>0.2184031828903329</v>
+        <v>0.2186262190071236</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3074077097410777</v>
+        <v>0.3034665852572177</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2261233904009408</v>
+        <v>0.2280233904009408</v>
       </c>
       <c r="C80">
-        <v>-788.6836751956178</v>
+        <v>-810.8311513512263</v>
       </c>
       <c r="D80">
-        <v>387.3183248043824</v>
+        <v>383.2798486487739</v>
       </c>
       <c r="E80">
-        <v>840.6020000000002</v>
+        <v>858.7110000000001</v>
       </c>
       <c r="F80">
-        <v>1412.502</v>
+        <v>1430.611</v>
       </c>
       <c r="G80">
         <v>236.5</v>
@@ -7853,37 +7853,37 @@
         <v>101.075</v>
       </c>
       <c r="M80">
-        <v>333.0679716000001</v>
+        <v>337.3380738</v>
       </c>
       <c r="N80">
-        <v>-231.9929716000001</v>
+        <v>-236.2630738</v>
       </c>
       <c r="O80">
-        <v>-55.67831318400002</v>
+        <v>-56.70313771200001</v>
       </c>
       <c r="P80">
-        <v>-176.3146584160001</v>
+        <v>-179.559936088</v>
       </c>
       <c r="Q80">
-        <v>-100.5146584160001</v>
+        <v>-103.759936088</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2527042707972021</v>
+        <v>0.2625568551208784</v>
       </c>
       <c r="T80">
-        <v>4.254169578108704</v>
+        <v>4.456749081828167</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07283198046173225</v>
+        <v>0.07191005665841919</v>
       </c>
       <c r="W80">
-        <v>0.2186262190071236</v>
+        <v>0.2188436086399448</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3034665852572177</v>
+        <v>0.2996252360767466</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2280233904009408</v>
+        <v>0.2299233904009408</v>
       </c>
       <c r="C81">
-        <v>-810.8311513512263</v>
+        <v>-832.895280087705</v>
       </c>
       <c r="D81">
-        <v>383.2798486487739</v>
+        <v>379.3247199122952</v>
       </c>
       <c r="E81">
-        <v>858.7110000000001</v>
+        <v>876.8200000000003</v>
       </c>
       <c r="F81">
-        <v>1430.611</v>
+        <v>1448.72</v>
       </c>
       <c r="G81">
         <v>236.5</v>
@@ -7935,37 +7935,37 @@
         <v>101.075</v>
       </c>
       <c r="M81">
-        <v>337.3380738</v>
+        <v>341.6081760000001</v>
       </c>
       <c r="N81">
-        <v>-236.2630738</v>
+        <v>-240.5331760000001</v>
       </c>
       <c r="O81">
-        <v>-56.70313771200001</v>
+        <v>-57.72796224000002</v>
       </c>
       <c r="P81">
-        <v>-179.559936088</v>
+        <v>-182.8052137600001</v>
       </c>
       <c r="Q81">
-        <v>-103.759936088</v>
+        <v>-107.0052137600001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2625568551208784</v>
+        <v>0.2733946978769223</v>
       </c>
       <c r="T81">
-        <v>4.456749081828167</v>
+        <v>4.679586535919575</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07191005665841919</v>
+        <v>0.07101118095018896</v>
       </c>
       <c r="W81">
-        <v>0.2188436086399448</v>
+        <v>0.2190555635319454</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2996252360767466</v>
+        <v>0.2958799206257873</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2299233904009408</v>
+        <v>0.2318233904009408</v>
       </c>
       <c r="C82">
-        <v>-832.895280087705</v>
+        <v>-854.8786152789945</v>
       </c>
       <c r="D82">
-        <v>379.3247199122952</v>
+        <v>375.4503847210057</v>
       </c>
       <c r="E82">
-        <v>876.8200000000003</v>
+        <v>894.9290000000002</v>
       </c>
       <c r="F82">
-        <v>1448.72</v>
+        <v>1466.829</v>
       </c>
       <c r="G82">
         <v>236.5</v>
@@ -8017,37 +8017,37 @@
         <v>101.075</v>
       </c>
       <c r="M82">
-        <v>341.6081760000001</v>
+        <v>345.8782782000001</v>
       </c>
       <c r="N82">
-        <v>-240.5331760000001</v>
+        <v>-244.8032782000001</v>
       </c>
       <c r="O82">
-        <v>-57.72796224000002</v>
+        <v>-58.75278676800001</v>
       </c>
       <c r="P82">
-        <v>-182.8052137600001</v>
+        <v>-186.0504914320001</v>
       </c>
       <c r="Q82">
-        <v>-107.0052137600001</v>
+        <v>-110.2504914320001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2733946978769223</v>
+        <v>0.2853733661862341</v>
       </c>
       <c r="T82">
-        <v>4.679586535919575</v>
+        <v>4.92588056412587</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07101118095018896</v>
+        <v>0.07013449970389032</v>
       </c>
       <c r="W82">
-        <v>0.2190555635319454</v>
+        <v>0.2192622849698227</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2958799206257873</v>
+        <v>0.292227082099543</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2318233904009408</v>
+        <v>0.2337233904009408</v>
       </c>
       <c r="C83">
-        <v>-854.8786152789945</v>
+        <v>-876.7836075152347</v>
       </c>
       <c r="D83">
-        <v>375.4503847210057</v>
+        <v>371.6543924847654</v>
       </c>
       <c r="E83">
-        <v>894.9290000000002</v>
+        <v>913.0380000000001</v>
       </c>
       <c r="F83">
-        <v>1466.829</v>
+        <v>1484.938</v>
       </c>
       <c r="G83">
         <v>236.5</v>
@@ -8099,37 +8099,37 @@
         <v>101.075</v>
       </c>
       <c r="M83">
-        <v>345.8782782000001</v>
+        <v>350.1483804000001</v>
       </c>
       <c r="N83">
-        <v>-244.8032782000001</v>
+        <v>-249.0733804000001</v>
       </c>
       <c r="O83">
-        <v>-58.75278676800001</v>
+        <v>-59.77761129600002</v>
       </c>
       <c r="P83">
-        <v>-186.0504914320001</v>
+        <v>-189.295769104</v>
       </c>
       <c r="Q83">
-        <v>-110.2504914320001</v>
+        <v>-113.495769104</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2853733661862341</v>
+        <v>0.2986829976410248</v>
       </c>
       <c r="T83">
-        <v>4.92588056412587</v>
+        <v>5.199540595466195</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07013449970389032</v>
+        <v>0.0692792009270136</v>
       </c>
       <c r="W83">
-        <v>0.2192622849698227</v>
+        <v>0.2194639644214102</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.292227082099543</v>
+        <v>0.28866333719589</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2337233904009408</v>
+        <v>0.2356233904009409</v>
       </c>
       <c r="C84">
-        <v>-876.7836075152347</v>
+        <v>-898.61260927176</v>
       </c>
       <c r="D84">
-        <v>371.6543924847654</v>
+        <v>367.9343907282403</v>
       </c>
       <c r="E84">
-        <v>913.0380000000001</v>
+        <v>931.1470000000003</v>
       </c>
       <c r="F84">
-        <v>1484.938</v>
+        <v>1503.047</v>
       </c>
       <c r="G84">
         <v>236.5</v>
@@ -8181,37 +8181,37 @@
         <v>101.075</v>
       </c>
       <c r="M84">
-        <v>350.1483804000001</v>
+        <v>354.4184826000001</v>
       </c>
       <c r="N84">
-        <v>-249.0733804000001</v>
+        <v>-253.3434826000001</v>
       </c>
       <c r="O84">
-        <v>-59.77761129600002</v>
+        <v>-60.80243582400001</v>
       </c>
       <c r="P84">
-        <v>-189.295769104</v>
+        <v>-192.5410467760001</v>
       </c>
       <c r="Q84">
-        <v>-113.495769104</v>
+        <v>-116.7410467760001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2986829976410248</v>
+        <v>0.3135584680904969</v>
       </c>
       <c r="T84">
-        <v>5.199540595466195</v>
+        <v>5.505395924611266</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0692792009270136</v>
+        <v>0.06844451175921827</v>
       </c>
       <c r="W84">
-        <v>0.2194639644214102</v>
+        <v>0.2196607841271764</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.28866333719589</v>
+        <v>0.2851854656634094</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2356233904009409</v>
+        <v>0.2375233904009408</v>
       </c>
       <c r="C85">
-        <v>-898.61260927176</v>
+        <v>-920.3678797707414</v>
       </c>
       <c r="D85">
-        <v>367.9343907282403</v>
+        <v>364.2881202292587</v>
       </c>
       <c r="E85">
-        <v>931.1470000000003</v>
+        <v>949.2560000000002</v>
       </c>
       <c r="F85">
-        <v>1503.047</v>
+        <v>1521.156</v>
       </c>
       <c r="G85">
         <v>236.5</v>
@@ -8263,37 +8263,37 @@
         <v>101.075</v>
       </c>
       <c r="M85">
-        <v>354.4184826000001</v>
+        <v>358.6885848000001</v>
       </c>
       <c r="N85">
-        <v>-253.3434826000001</v>
+        <v>-257.6135848000001</v>
       </c>
       <c r="O85">
-        <v>-60.80243582400001</v>
+        <v>-61.82726035200002</v>
       </c>
       <c r="P85">
-        <v>-192.5410467760001</v>
+        <v>-195.786324448</v>
       </c>
       <c r="Q85">
-        <v>-116.7410467760001</v>
+        <v>-119.986324448</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3135584680904969</v>
+        <v>0.3302933723461531</v>
       </c>
       <c r="T85">
-        <v>5.505395924611266</v>
+        <v>5.849483169899472</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06844451175921827</v>
+        <v>0.0676296961430371</v>
       </c>
       <c r="W85">
-        <v>0.2196607841271764</v>
+        <v>0.2198529176494718</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2851854656634094</v>
+        <v>0.2817904005959879</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2375233904009408</v>
+        <v>0.2394233904009408</v>
       </c>
       <c r="C86">
-        <v>-920.3678797707411</v>
+        <v>-942.0515895565907</v>
       </c>
       <c r="D86">
-        <v>364.2881202292589</v>
+        <v>360.7134104434094</v>
       </c>
       <c r="E86">
-        <v>949.256</v>
+        <v>967.3650000000001</v>
       </c>
       <c r="F86">
-        <v>1521.156</v>
+        <v>1539.265</v>
       </c>
       <c r="G86">
         <v>236.5</v>
@@ -8345,37 +8345,37 @@
         <v>101.075</v>
       </c>
       <c r="M86">
-        <v>358.6885848</v>
+        <v>362.9586870000001</v>
       </c>
       <c r="N86">
-        <v>-257.6135848</v>
+        <v>-261.8836870000001</v>
       </c>
       <c r="O86">
-        <v>-61.827260352</v>
+        <v>-62.85208488000001</v>
       </c>
       <c r="P86">
-        <v>-195.786324448</v>
+        <v>-199.0316021200001</v>
       </c>
       <c r="Q86">
-        <v>-119.986324448</v>
+        <v>-123.2316021200001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3302933723461529</v>
+        <v>0.3492595971692297</v>
       </c>
       <c r="T86">
-        <v>5.849483169899467</v>
+        <v>6.239448714559432</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06762969614303711</v>
+        <v>0.06683405265900137</v>
       </c>
       <c r="W86">
-        <v>0.2198529176494718</v>
+        <v>0.2200405303830075</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2817904005959879</v>
+        <v>0.2784752194125056</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2394233904009408</v>
+        <v>0.2413233904009408</v>
       </c>
       <c r="C87">
-        <v>-942.0515895565907</v>
+        <v>-963.6658248045939</v>
       </c>
       <c r="D87">
-        <v>360.7134104434094</v>
+        <v>357.2081751954062</v>
       </c>
       <c r="E87">
-        <v>967.3650000000001</v>
+        <v>985.474</v>
       </c>
       <c r="F87">
-        <v>1539.265</v>
+        <v>1557.374</v>
       </c>
       <c r="G87">
         <v>236.5</v>
@@ -8427,37 +8427,37 @@
         <v>101.075</v>
       </c>
       <c r="M87">
-        <v>362.9586870000001</v>
+        <v>367.2287892</v>
       </c>
       <c r="N87">
-        <v>-261.8836870000001</v>
+        <v>-266.1537892</v>
       </c>
       <c r="O87">
-        <v>-62.85208488000001</v>
+        <v>-63.876909408</v>
       </c>
       <c r="P87">
-        <v>-199.0316021200001</v>
+        <v>-202.276879792</v>
       </c>
       <c r="Q87">
-        <v>-123.2316021200001</v>
+        <v>-126.476879792</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3492595971692297</v>
+        <v>0.3709352826813176</v>
       </c>
       <c r="T87">
-        <v>6.239448714559432</v>
+        <v>6.685123622742249</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06683405265900137</v>
+        <v>0.06605691251180369</v>
       </c>
       <c r="W87">
-        <v>0.2200405303830075</v>
+        <v>0.2202237800297167</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2784752194125056</v>
+        <v>0.2752371354658487</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2413233904009408</v>
+        <v>0.2432233904009408</v>
       </c>
       <c r="C88">
-        <v>-963.6658248045939</v>
+        <v>-985.2125913807477</v>
       </c>
       <c r="D88">
-        <v>357.2081751954062</v>
+        <v>353.7704086192525</v>
       </c>
       <c r="E88">
-        <v>985.474</v>
+        <v>1003.583</v>
       </c>
       <c r="F88">
-        <v>1557.374</v>
+        <v>1575.483</v>
       </c>
       <c r="G88">
         <v>236.5</v>
@@ -8509,37 +8509,37 @@
         <v>101.075</v>
       </c>
       <c r="M88">
-        <v>367.2287892</v>
+        <v>371.4988914</v>
       </c>
       <c r="N88">
-        <v>-266.1537892</v>
+        <v>-270.4238914000001</v>
       </c>
       <c r="O88">
-        <v>-63.876909408</v>
+        <v>-64.90173393600001</v>
       </c>
       <c r="P88">
-        <v>-202.276879792</v>
+        <v>-205.522157464</v>
       </c>
       <c r="Q88">
-        <v>-126.476879792</v>
+        <v>-129.722157464</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3709352826813176</v>
+        <v>0.3959456890414189</v>
       </c>
       <c r="T88">
-        <v>6.685123622742249</v>
+        <v>7.199363901414729</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06605691251180369</v>
+        <v>0.06529763765534617</v>
       </c>
       <c r="W88">
-        <v>0.2202237800297167</v>
+        <v>0.2204028170408694</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2752371354658487</v>
+        <v>0.272073490230609</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2432233904009408</v>
+        <v>0.2451233904009408</v>
       </c>
       <c r="C89">
-        <v>-985.2125913807477</v>
+        <v>-1006.693818669399</v>
       </c>
       <c r="D89">
-        <v>353.7704086192525</v>
+        <v>350.3981813306009</v>
       </c>
       <c r="E89">
-        <v>1003.583</v>
+        <v>1021.692</v>
       </c>
       <c r="F89">
-        <v>1575.483</v>
+        <v>1593.592</v>
       </c>
       <c r="G89">
         <v>236.5</v>
@@ -8591,37 +8591,37 @@
         <v>101.075</v>
       </c>
       <c r="M89">
-        <v>371.4988914</v>
+        <v>375.7689936</v>
       </c>
       <c r="N89">
-        <v>-270.4238914000001</v>
+        <v>-274.6939936000001</v>
       </c>
       <c r="O89">
-        <v>-64.90173393600001</v>
+        <v>-65.92655846400001</v>
       </c>
       <c r="P89">
-        <v>-205.522157464</v>
+        <v>-208.767435136</v>
       </c>
       <c r="Q89">
-        <v>-129.722157464</v>
+        <v>-132.9674351360001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3959456890414189</v>
+        <v>0.4251244964615372</v>
       </c>
       <c r="T89">
-        <v>7.199363901414729</v>
+        <v>7.799310893199292</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06529763765534617</v>
+        <v>0.06455561904562633</v>
       </c>
       <c r="W89">
-        <v>0.2204028170408694</v>
+        <v>0.2205777850290413</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.272073490230609</v>
+        <v>0.268981746023443</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2451233904009408</v>
+        <v>0.2470233904009408</v>
       </c>
       <c r="C90">
-        <v>-1006.693818669399</v>
+        <v>-1028.111363184038</v>
       </c>
       <c r="D90">
-        <v>350.3981813306009</v>
+        <v>347.089636815962</v>
       </c>
       <c r="E90">
-        <v>1021.692</v>
+        <v>1039.801</v>
       </c>
       <c r="F90">
-        <v>1593.592</v>
+        <v>1611.701</v>
       </c>
       <c r="G90">
         <v>236.5</v>
@@ -8673,37 +8673,37 @@
         <v>101.075</v>
       </c>
       <c r="M90">
-        <v>375.7689936</v>
+        <v>380.0390958</v>
       </c>
       <c r="N90">
-        <v>-274.6939936000001</v>
+        <v>-278.9640958000001</v>
       </c>
       <c r="O90">
-        <v>-65.92655846400001</v>
+        <v>-66.95138299200001</v>
       </c>
       <c r="P90">
-        <v>-208.767435136</v>
+        <v>-212.0127128080001</v>
       </c>
       <c r="Q90">
-        <v>-132.9674351360001</v>
+        <v>-136.212712808</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4251244964615372</v>
+        <v>0.4596085415944042</v>
       </c>
       <c r="T90">
-        <v>7.799310893199292</v>
+        <v>8.508339156217408</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06455561904562633</v>
+        <v>0.06383027501140581</v>
       </c>
       <c r="W90">
-        <v>0.2205777850290413</v>
+        <v>0.2207488211523105</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.268981746023443</v>
+        <v>0.2659594792141908</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2470233904009408</v>
+        <v>0.2489233904009408</v>
       </c>
       <c r="C91">
-        <v>-1028.111363184038</v>
+        <v>-1049.467011975439</v>
       </c>
       <c r="D91">
-        <v>347.089636815962</v>
+        <v>343.8429880245615</v>
       </c>
       <c r="E91">
-        <v>1039.801</v>
+        <v>1057.91</v>
       </c>
       <c r="F91">
-        <v>1611.701</v>
+        <v>1629.81</v>
       </c>
       <c r="G91">
         <v>236.5</v>
@@ -8755,37 +8755,37 @@
         <v>101.075</v>
       </c>
       <c r="M91">
-        <v>380.0390958</v>
+        <v>384.309198</v>
       </c>
       <c r="N91">
-        <v>-278.9640958000001</v>
+        <v>-283.234198</v>
       </c>
       <c r="O91">
-        <v>-66.95138299200001</v>
+        <v>-67.97620752</v>
       </c>
       <c r="P91">
-        <v>-212.0127128080001</v>
+        <v>-215.25799048</v>
       </c>
       <c r="Q91">
-        <v>-136.212712808</v>
+        <v>-139.45799048</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4596085415944042</v>
+        <v>0.5009893957538446</v>
       </c>
       <c r="T91">
-        <v>8.508339156217408</v>
+        <v>9.35917307183915</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06383027501140581</v>
+        <v>0.0631210497335013</v>
       </c>
       <c r="W91">
-        <v>0.2207488211523105</v>
+        <v>0.2209160564728404</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2659594792141908</v>
+        <v>0.2630043738895887</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2489233904009408</v>
+        <v>0.2508233904009408</v>
       </c>
       <c r="C92">
-        <v>-1049.467011975439</v>
+        <v>-1070.762485850293</v>
       </c>
       <c r="D92">
-        <v>343.8429880245615</v>
+        <v>340.6565141497072</v>
       </c>
       <c r="E92">
-        <v>1057.91</v>
+        <v>1076.019</v>
       </c>
       <c r="F92">
-        <v>1629.81</v>
+        <v>1647.919</v>
       </c>
       <c r="G92">
         <v>236.5</v>
@@ -8837,37 +8837,37 @@
         <v>101.075</v>
       </c>
       <c r="M92">
-        <v>384.309198</v>
+        <v>388.5793002</v>
       </c>
       <c r="N92">
-        <v>-283.234198</v>
+        <v>-287.5043002</v>
       </c>
       <c r="O92">
-        <v>-67.97620752</v>
+        <v>-69.00103204800001</v>
       </c>
       <c r="P92">
-        <v>-215.25799048</v>
+        <v>-218.503268152</v>
       </c>
       <c r="Q92">
-        <v>-139.45799048</v>
+        <v>-142.703268152</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5009893957538446</v>
+        <v>0.5515659952820496</v>
       </c>
       <c r="T92">
-        <v>9.35917307183915</v>
+        <v>10.39908119093239</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0631210497335013</v>
+        <v>0.06242741182434194</v>
       </c>
       <c r="W92">
-        <v>0.2209160564728404</v>
+        <v>0.2210796162918202</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2630043738895887</v>
+        <v>0.260114215934758</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2508233904009408</v>
+        <v>0.2527233904009408</v>
       </c>
       <c r="C93">
-        <v>-1070.762485850293</v>
+        <v>-1091.999442412528</v>
       </c>
       <c r="D93">
-        <v>340.6565141497072</v>
+        <v>337.5285575874725</v>
       </c>
       <c r="E93">
-        <v>1076.019</v>
+        <v>1094.128</v>
       </c>
       <c r="F93">
-        <v>1647.919</v>
+        <v>1666.028</v>
       </c>
       <c r="G93">
         <v>236.5</v>
@@ -8919,37 +8919,37 @@
         <v>101.075</v>
       </c>
       <c r="M93">
-        <v>388.5793002</v>
+        <v>392.8494024000001</v>
       </c>
       <c r="N93">
-        <v>-287.5043002</v>
+        <v>-291.7744024000001</v>
       </c>
       <c r="O93">
-        <v>-69.00103204800001</v>
+        <v>-70.02585657600002</v>
       </c>
       <c r="P93">
-        <v>-218.503268152</v>
+        <v>-221.7485458240001</v>
       </c>
       <c r="Q93">
-        <v>-142.703268152</v>
+        <v>-145.9485458240001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5515659952820496</v>
+        <v>0.6147867446923061</v>
       </c>
       <c r="T93">
-        <v>10.39908119093239</v>
+        <v>11.69896633979894</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06242741182434194</v>
+        <v>0.06174885300016431</v>
       </c>
       <c r="W93">
-        <v>0.2210796162918202</v>
+        <v>0.2212396204625613</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.260114215934758</v>
+        <v>0.2572868875006846</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2527233904009408</v>
+        <v>0.2546233904009408</v>
       </c>
       <c r="C94">
-        <v>-1091.999442412528</v>
+        <v>-1113.179478938584</v>
       </c>
       <c r="D94">
-        <v>337.5285575874725</v>
+        <v>334.4575210614162</v>
       </c>
       <c r="E94">
-        <v>1094.128</v>
+        <v>1112.237</v>
       </c>
       <c r="F94">
-        <v>1666.028</v>
+        <v>1684.137</v>
       </c>
       <c r="G94">
         <v>236.5</v>
@@ -9001,37 +9001,37 @@
         <v>101.075</v>
       </c>
       <c r="M94">
-        <v>392.8494024000001</v>
+        <v>397.1195046000001</v>
       </c>
       <c r="N94">
-        <v>-291.7744024000001</v>
+        <v>-296.0445046000001</v>
       </c>
       <c r="O94">
-        <v>-70.02585657600002</v>
+        <v>-71.05068110400002</v>
       </c>
       <c r="P94">
-        <v>-221.7485458240001</v>
+        <v>-224.9938234960001</v>
       </c>
       <c r="Q94">
-        <v>-145.9485458240001</v>
+        <v>-149.193823496</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6147867446923061</v>
+        <v>0.6960705653626356</v>
       </c>
       <c r="T94">
-        <v>11.69896633979894</v>
+        <v>13.37024724548451</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06174885300016431</v>
+        <v>0.06108488683887222</v>
       </c>
       <c r="W94">
-        <v>0.2212396204625613</v>
+        <v>0.2213961836833939</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2572868875006846</v>
+        <v>0.2545203618286342</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2546233904009408</v>
+        <v>0.2565233904009408</v>
       </c>
       <c r="C95">
-        <v>-1113.179478938584</v>
+        <v>-1134.30413509715</v>
       </c>
       <c r="D95">
-        <v>334.4575210614162</v>
+        <v>331.4418649028495</v>
       </c>
       <c r="E95">
-        <v>1112.237</v>
+        <v>1130.346</v>
       </c>
       <c r="F95">
-        <v>1684.137</v>
+        <v>1702.246</v>
       </c>
       <c r="G95">
         <v>236.5</v>
@@ -9083,37 +9083,37 @@
         <v>101.075</v>
       </c>
       <c r="M95">
-        <v>397.1195046000001</v>
+        <v>401.3896068</v>
       </c>
       <c r="N95">
-        <v>-296.0445046000001</v>
+        <v>-300.3146068</v>
       </c>
       <c r="O95">
-        <v>-71.05068110400002</v>
+        <v>-72.075505632</v>
       </c>
       <c r="P95">
-        <v>-224.9938234960001</v>
+        <v>-228.239101168</v>
       </c>
       <c r="Q95">
-        <v>-149.193823496</v>
+        <v>-152.439101168</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6960705653626356</v>
+        <v>0.804448992923075</v>
       </c>
       <c r="T95">
-        <v>13.37024724548451</v>
+        <v>15.5986217863986</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06108488683887222</v>
+        <v>0.0604350476171821</v>
       </c>
       <c r="W95">
-        <v>0.2213961836833939</v>
+        <v>0.2215494157718685</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2545203618286342</v>
+        <v>0.2518126984049254</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2565233904009408</v>
+        <v>0.2584233904009409</v>
       </c>
       <c r="C96">
-        <v>-1134.30413509715</v>
+        <v>-1155.374895523075</v>
       </c>
       <c r="D96">
-        <v>331.4418649028495</v>
+        <v>328.4801044769249</v>
       </c>
       <c r="E96">
-        <v>1130.346</v>
+        <v>1148.455</v>
       </c>
       <c r="F96">
-        <v>1702.246</v>
+        <v>1720.355</v>
       </c>
       <c r="G96">
         <v>236.5</v>
@@ -9165,37 +9165,37 @@
         <v>101.075</v>
       </c>
       <c r="M96">
-        <v>401.3896068</v>
+        <v>405.6597090000001</v>
       </c>
       <c r="N96">
-        <v>-300.3146068</v>
+        <v>-304.5847090000001</v>
       </c>
       <c r="O96">
-        <v>-72.075505632</v>
+        <v>-73.10033016000001</v>
       </c>
       <c r="P96">
-        <v>-228.239101168</v>
+        <v>-231.4843788400001</v>
       </c>
       <c r="Q96">
-        <v>-152.439101168</v>
+        <v>-155.6843788400001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.804448992923075</v>
+        <v>0.9561787915076904</v>
       </c>
       <c r="T96">
-        <v>15.5986217863986</v>
+        <v>18.71834614367832</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0604350476171821</v>
+        <v>0.05979888922121175</v>
       </c>
       <c r="W96">
-        <v>0.2215494157718685</v>
+        <v>0.2216994219216383</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2518126984049254</v>
+        <v>0.2491620384217156</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2584233904009409</v>
+        <v>0.2603233904009408</v>
       </c>
       <c r="C97">
-        <v>-1155.374895523075</v>
+        <v>-1176.393192254493</v>
       </c>
       <c r="D97">
-        <v>328.4801044769249</v>
+        <v>325.5708077455068</v>
       </c>
       <c r="E97">
-        <v>1148.455</v>
+        <v>1166.564</v>
       </c>
       <c r="F97">
-        <v>1720.355</v>
+        <v>1738.464</v>
       </c>
       <c r="G97">
         <v>236.5</v>
@@ -9247,37 +9247,37 @@
         <v>101.075</v>
       </c>
       <c r="M97">
-        <v>405.6597090000001</v>
+        <v>409.9298112000001</v>
       </c>
       <c r="N97">
-        <v>-304.5847090000001</v>
+        <v>-308.8548112000001</v>
       </c>
       <c r="O97">
-        <v>-73.10033016000001</v>
+        <v>-74.12515468800002</v>
       </c>
       <c r="P97">
-        <v>-231.4843788400001</v>
+        <v>-234.7296565120001</v>
       </c>
       <c r="Q97">
-        <v>-155.6843788400001</v>
+        <v>-158.9296565120001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9561787915076904</v>
+        <v>1.183773489384614</v>
       </c>
       <c r="T97">
-        <v>18.71834614367832</v>
+        <v>23.39793267959791</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05979888922121175</v>
+        <v>0.05917598412515746</v>
       </c>
       <c r="W97">
-        <v>0.2216994219216383</v>
+        <v>0.2218463029432879</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2491620384217156</v>
+        <v>0.2465666005214894</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2603233904009408</v>
+        <v>0.2622233904009408</v>
       </c>
       <c r="C98">
-        <v>-1176.393192254493</v>
+        <v>-1197.360407041585</v>
       </c>
       <c r="D98">
-        <v>325.5708077455068</v>
+        <v>322.7125929584153</v>
       </c>
       <c r="E98">
-        <v>1166.564</v>
+        <v>1184.673</v>
       </c>
       <c r="F98">
-        <v>1738.464</v>
+        <v>1756.573</v>
       </c>
       <c r="G98">
         <v>236.5</v>
@@ -9329,37 +9329,37 @@
         <v>101.075</v>
       </c>
       <c r="M98">
-        <v>409.9298112</v>
+        <v>414.1999134</v>
       </c>
       <c r="N98">
-        <v>-308.8548112</v>
+        <v>-313.1249134</v>
       </c>
       <c r="O98">
-        <v>-74.12515468800001</v>
+        <v>-75.14997921600001</v>
       </c>
       <c r="P98">
-        <v>-234.729656512</v>
+        <v>-237.974934184</v>
       </c>
       <c r="Q98">
-        <v>-158.929656512</v>
+        <v>-162.174934184</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.183773489384611</v>
+        <v>1.563097985846148</v>
       </c>
       <c r="T98">
-        <v>23.39793267959785</v>
+        <v>31.19724357279714</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05917598412515747</v>
+        <v>0.05856592243314554</v>
       </c>
       <c r="W98">
-        <v>0.2218463029432879</v>
+        <v>0.2219901554902643</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2465666005214895</v>
+        <v>0.244024676804773</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2622233904009408</v>
+        <v>0.2641233904009408</v>
       </c>
       <c r="C99">
-        <v>-1197.360407041585</v>
+        <v>-1218.277873534776</v>
       </c>
       <c r="D99">
-        <v>322.7125929584153</v>
+        <v>319.9041264652238</v>
       </c>
       <c r="E99">
-        <v>1184.673</v>
+        <v>1202.782</v>
       </c>
       <c r="F99">
-        <v>1756.573</v>
+        <v>1774.682</v>
       </c>
       <c r="G99">
         <v>236.5</v>
@@ -9411,37 +9411,37 @@
         <v>101.075</v>
       </c>
       <c r="M99">
-        <v>414.1999134</v>
+        <v>418.4700156</v>
       </c>
       <c r="N99">
-        <v>-313.1249134</v>
+        <v>-317.3950156</v>
       </c>
       <c r="O99">
-        <v>-75.14997921600001</v>
+        <v>-76.174803744</v>
       </c>
       <c r="P99">
-        <v>-237.974934184</v>
+        <v>-241.220211856</v>
       </c>
       <c r="Q99">
-        <v>-162.174934184</v>
+        <v>-165.420211856</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.563097985846148</v>
+        <v>2.321746978769221</v>
       </c>
       <c r="T99">
-        <v>31.19724357279714</v>
+        <v>46.79586535919571</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05856592243314554</v>
+        <v>0.0579683109797461</v>
       </c>
       <c r="W99">
-        <v>0.2219901554902643</v>
+        <v>0.2221310722709759</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.244024676804773</v>
+        <v>0.2415346290822754</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2641233904009408</v>
+        <v>0.2660233904009408</v>
       </c>
       <c r="C100">
-        <v>-1218.277873534776</v>
+        <v>-1239.146879359668</v>
       </c>
       <c r="D100">
-        <v>319.9041264652238</v>
+        <v>317.1441206403325</v>
       </c>
       <c r="E100">
-        <v>1202.782</v>
+        <v>1220.891</v>
       </c>
       <c r="F100">
-        <v>1774.682</v>
+        <v>1792.791</v>
       </c>
       <c r="G100">
         <v>236.5</v>
@@ -9493,37 +9493,37 @@
         <v>101.075</v>
       </c>
       <c r="M100">
-        <v>418.4700156</v>
+        <v>422.7401178000001</v>
       </c>
       <c r="N100">
-        <v>-317.3950156</v>
+        <v>-321.6651178000001</v>
       </c>
       <c r="O100">
-        <v>-76.174803744</v>
+        <v>-77.19962827200001</v>
       </c>
       <c r="P100">
-        <v>-241.220211856</v>
+        <v>-244.4654895280001</v>
       </c>
       <c r="Q100">
-        <v>-165.420211856</v>
+        <v>-168.6654895280001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.321746978769221</v>
+        <v>4.597693957538443</v>
       </c>
       <c r="T100">
-        <v>46.79586535919571</v>
+        <v>93.59173071839142</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0579683109797461</v>
+        <v>0.05738277248500118</v>
       </c>
       <c r="W100">
-        <v>0.2221310722709759</v>
+        <v>0.2222691422480367</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2415346290822754</v>
+        <v>0.2390948853541716</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2660233904009408</v>
-      </c>
-      <c r="C101">
-        <v>-1239.146879359668</v>
-      </c>
-      <c r="D101">
-        <v>317.1441206403325</v>
-      </c>
-      <c r="E101">
-        <v>1220.891</v>
-      </c>
-      <c r="F101">
-        <v>1792.791</v>
-      </c>
-      <c r="G101">
-        <v>236.5</v>
-      </c>
-      <c r="H101">
-        <v>1239</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>176.875</v>
-      </c>
-      <c r="K101">
-        <v>75.8</v>
-      </c>
-      <c r="L101">
-        <v>101.075</v>
-      </c>
-      <c r="M101">
-        <v>422.7401178000001</v>
-      </c>
-      <c r="N101">
-        <v>-321.6651178000001</v>
-      </c>
-      <c r="O101">
-        <v>-77.19962827200001</v>
-      </c>
-      <c r="P101">
-        <v>-244.4654895280001</v>
-      </c>
-      <c r="Q101">
-        <v>-168.6654895280001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.597693957538443</v>
-      </c>
-      <c r="T101">
-        <v>93.59173071839142</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05738277248500118</v>
-      </c>
-      <c r="W101">
-        <v>0.2222691422480367</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2390948853541716</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
